--- a/logs/final_winner_optimization/experiments_summary.xlsx
+++ b/logs/final_winner_optimization/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW39"/>
+  <dimension ref="A1:BW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>false.1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>false.2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -925,13 +925,9 @@
         <v>4000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4000.1</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Unnamed: 27</t>
-        </is>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>512</v>
       </c>
@@ -970,20 +966,14 @@
       <c r="AN2" t="n">
         <v>0.7646160822528379</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>13.36954740649872.1</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>13.36954740649872.2</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.764616082252838.1</t>
-        </is>
+      <c r="AO2" t="n">
+        <v>1336954740649870</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1336954740649870</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.7646160822528379</v>
       </c>
       <c r="AR2" t="n">
         <v>96.29683756211355</v>
@@ -1005,20 +995,14 @@
       <c r="AW2" t="n">
         <v>0.696481874958176</v>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.04179946006517127.1</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.04179946006517127.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.696481874958176.1</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>0.0417994600651712</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.0417994600651712</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.696481874958176</v>
       </c>
       <c r="BA2" t="n">
         <v>0.2326406428811708</v>
@@ -1032,20 +1016,14 @@
       <c r="BD2" t="n">
         <v>0.8355435748117486</v>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.04746509751204102.1</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.04746509751204102.2</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.8355435748117486.1</t>
-        </is>
+      <c r="BE2" t="n">
+        <v>0.047465097512041</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.047465097512041</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.835543574811748</v>
       </c>
       <c r="BH2" t="n">
         <v>0.2006380945437835</v>
@@ -1059,20 +1037,14 @@
       <c r="BK2" t="n">
         <v>0.6781650091535286</v>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.08016446999278473.1</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.08016446999278473.2</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.6781650091535286.1</t>
-        </is>
+      <c r="BL2" t="n">
+        <v>0.0801644699927847</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.0801644699927847</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.678165009153528</v>
       </c>
       <c r="BO2" t="n">
         <v>0.1752503629696627</v>
@@ -1086,20 +1058,14 @@
       <c r="BR2" t="n">
         <v>0.848273870087896</v>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>53.3087605984251.1</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>53.3087605984251.2</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.848273870087896.1</t>
-        </is>
+      <c r="BS2" t="n">
+        <v>53.3087605984251</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>53.3087605984251</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.848273870087896</v>
       </c>
       <c r="BV2" t="n">
         <v>384.5788211480605</v>
@@ -2170,11 +2136,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46070.07273148148</v>
+        <v>46070.57792824074</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>02-17_01-44-44_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-17_13-52-13_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2435,19 +2401,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46070.57784722222</v>
+        <v>46070.57796296296</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02-17_13-52-06_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-17_13-52-16_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Final (Last Iteration)</t>
+          <t>Best (Lowest Val Loss)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2561,7 +2527,7 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AF8" t="n">
         <v>180</v>
@@ -2573,37 +2539,37 @@
         <v>120</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.07747318236880141</v>
+        <v>0.124712634239408</v>
       </c>
       <c r="AJ8" t="n">
-        <v>10.36693594382798</v>
+        <v>10.24891702410613</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.7676869412587883</v>
+        <v>0.787850224007417</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.1313859225998066</v>
+        <v>0.06087001477968185</v>
       </c>
       <c r="AM8" t="n">
-        <v>13.36954740649872</v>
+        <v>12.69550708888744</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.7646160822528379</v>
+        <v>0.790151413234965</v>
       </c>
       <c r="AO8" t="n">
-        <v>13.36954740649872</v>
+        <v>12.69550708888744</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.36954740649872</v>
+        <v>12.69550708888744</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7646160822528379</v>
+        <v>0.790151413234965</v>
       </c>
       <c r="AR8" t="n">
-        <v>96.29683756211355</v>
+        <v>80.10151529294306</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.04564847515771711</v>
+        <v>0.1276246851708594</v>
       </c>
       <c r="AT8" t="n">
         <v>0.8</v>
@@ -2614,101 +2580,101 @@
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>0.04179946006517127</v>
+        <v>0.04485597879043379</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.696481874958176</v>
+        <v>0.6742875970607948</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.04179946006517127</v>
+        <v>0.04485597879043379</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.04179946006517127</v>
+        <v>0.04485597879043379</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.696481874958176</v>
+        <v>0.6742875970607948</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2326406428811708</v>
+        <v>0.1529031040334653</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.6892718620222729</v>
+        <v>-0.1102742326564587</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.04746509751204102</v>
+        <v>0.03760378228478881</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.8355435748117486</v>
+        <v>0.8697109258746418</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.04746509751204102</v>
+        <v>0.03760378228478881</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.04746509751204102</v>
+        <v>0.03760378228478881</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.8355435748117486</v>
+        <v>0.8697109258746418</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.2006380945437835</v>
+        <v>0.2100041245098935</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.3048318550934713</v>
+        <v>0.2723805616764139</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.08016446999278473</v>
+        <v>0.05959687030543954</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6781650091535286</v>
+        <v>0.7607374163272604</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.08016446999278473</v>
+        <v>0.05959687030543954</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.08016446999278473</v>
+        <v>0.05959687030543954</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.6781650091535286</v>
+        <v>0.7607374163272604</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.1752503629696627</v>
+        <v>0.1846306963069071</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.2964252247004356</v>
+        <v>0.258766153368702</v>
       </c>
       <c r="BQ8" t="n">
-        <v>53.3087605984251</v>
+        <v>50.6399717241691</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.848273870087896</v>
+        <v>0.8558697136771636</v>
       </c>
       <c r="BS8" t="n">
-        <v>53.3087605984251</v>
+        <v>50.6399717241691</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.3087605984251</v>
+        <v>50.6399717241691</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.848273870087896</v>
+        <v>0.8558697136771636</v>
       </c>
       <c r="BV8" t="n">
-        <v>384.5788211480605</v>
+        <v>319.8585232469213</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0.09457911840250666</v>
+        <v>0.0896262582947791</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46070.57787037037</v>
+        <v>46070.91962962963</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>02-17_13-52-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-17_22-04-16_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2826,7 +2792,7 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AF9" t="n">
         <v>180</v>
@@ -2838,37 +2804,37 @@
         <v>120</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0683298249277579</v>
+        <v>0.1422839026489602</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.556826886986359</v>
+        <v>14.43607972075677</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.7923658090319246</v>
+        <v>0.7391301085486564</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1936571846294888</v>
+        <v>-0.3540292039091948</v>
       </c>
       <c r="AM9" t="n">
-        <v>11.88127461092575</v>
+        <v>17.53605798652396</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.7996013374610866</v>
+        <v>0.7483259603977086</v>
       </c>
       <c r="AO9" t="n">
-        <v>11.88127461092575</v>
+        <v>17.53605798652396</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.88127461092575</v>
+        <v>17.53605798652396</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.7996013374610866</v>
+        <v>0.7483259603977086</v>
       </c>
       <c r="AR9" t="n">
-        <v>69.6233975435446</v>
+        <v>121.5809207744965</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.2591163014073077</v>
+        <v>-0.2063437040655124</v>
       </c>
       <c r="AT9" t="n">
         <v>0.8</v>
@@ -2879,101 +2845,101 @@
         </is>
       </c>
       <c r="AV9" t="n">
-        <v>0.04268508458669007</v>
+        <v>0.06690506576282984</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.690051095856165</v>
+        <v>0.5141827170859932</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.04268508458669007</v>
+        <v>0.06690506576282984</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.04268508458669007</v>
+        <v>0.06690506576282984</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.690051095856165</v>
+        <v>0.5141827170859932</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.1053350496163025</v>
+        <v>0.2421736560888115</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.2351313459341304</v>
+        <v>-0.7584938637005421</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0348922913372821</v>
+        <v>0.03601662974652821</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.8791056628820637</v>
+        <v>0.8752100704324842</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0348922913372821</v>
+        <v>0.03601662974652821</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0348922913372821</v>
+        <v>0.03601662974652821</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.8791056628820637</v>
+        <v>0.8752100704324842</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2091696208792715</v>
+        <v>0.2267518140630561</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.2752719385215555</v>
+        <v>0.2143533943799171</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0587529775623883</v>
+        <v>0.04903963060016262</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7641253787657291</v>
+        <v>0.8031213944689186</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0587529775623883</v>
+        <v>0.04903963060016262</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0587529775623883</v>
+        <v>0.04903963060016262</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.7641253787657291</v>
+        <v>0.8031213944689186</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1700446143357134</v>
+        <v>0.2239387950151985</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.317324658877533</v>
+        <v>0.100956570281409</v>
       </c>
       <c r="BQ9" t="n">
-        <v>47.38876809021656</v>
+        <v>69.99227061998641</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.86512321234039</v>
+        <v>0.8007896596034361</v>
       </c>
       <c r="BS9" t="n">
-        <v>47.38876809021656</v>
+        <v>69.99227061998641</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.38876809021656</v>
+        <v>69.99227061998641</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.86512321234039</v>
+        <v>0.8007896596034361</v>
       </c>
       <c r="BV9" t="n">
-        <v>278.0090408893465</v>
+        <v>485.6308188328184</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.2087372622960106</v>
+        <v>-0.3821909172228333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46070.57787037037</v>
+        <v>46071.25741898148</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>02-17_13-52-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-18_06-10-41_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3091,7 +3057,7 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AF10" t="n">
         <v>180</v>
@@ -3103,37 +3069,37 @@
         <v>120</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.07386345300842626</v>
+        <v>0.1468068008913335</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.87529985347638</v>
+        <v>11.89758449108911</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7614996210569579</v>
+        <v>0.7348544171690099</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.2466432066726592</v>
+        <v>-0.1824293941514002</v>
       </c>
       <c r="AM10" t="n">
-        <v>15.68184304215005</v>
+        <v>20.44376784822072</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.7724030300909095</v>
+        <v>0.7074937730035297</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.68184304215005</v>
+        <v>20.44376784822072</v>
       </c>
       <c r="AP10" t="n">
-        <v>15.68184304215005</v>
+        <v>20.44376784822072</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.7724030300909095</v>
+        <v>0.7074937730035297</v>
       </c>
       <c r="AR10" t="n">
-        <v>119.696370602724</v>
+        <v>128.3682595232955</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.1577455042266045</v>
+        <v>-0.2084005890128823</v>
       </c>
       <c r="AT10" t="n">
         <v>0.8</v>
@@ -3144,101 +3110,101 @@
         </is>
       </c>
       <c r="AV10" t="n">
-        <v>0.06059290810233586</v>
+        <v>0.05135137626833674</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5600171430593055</v>
+        <v>0.6271226130916072</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.06059290810233586</v>
+        <v>0.05135137626833674</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.06059290810233586</v>
+        <v>0.05135137626833674</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5600171430593055</v>
+        <v>0.6271226130916072</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2331920468843694</v>
+        <v>0.3138708149551491</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.6932757680280071</v>
+        <v>-1.279107938523697</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.03287111477907901</v>
+        <v>0.0564611151710727</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.8861086079692839</v>
+        <v>0.8043742950107449</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03287111477907901</v>
+        <v>0.0564611151710727</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.03287111477907901</v>
+        <v>0.0564611151710727</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.8861086079692839</v>
+        <v>0.8043742950107449</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.2193291720360637</v>
+        <v>0.1650953338199602</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.2400712636606358</v>
+        <v>0.4279799297072132</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.04443013607364577</v>
+        <v>0.09199834214943828</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.8216270570009847</v>
+        <v>0.6306557555208694</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.04443013607364577</v>
+        <v>0.09199834214943828</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04443013607364577</v>
+        <v>0.09199834214943828</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.8216270570009847</v>
+        <v>0.6306557555208694</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2034872001138056</v>
+        <v>0.1302153402852377</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1830632549320773</v>
+        <v>0.4772265961149423</v>
       </c>
       <c r="BQ10" t="n">
-        <v>62.5894780096449</v>
+        <v>81.57526055929397</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.8218593123340648</v>
+        <v>0.7678224283909009</v>
       </c>
       <c r="BS10" t="n">
-        <v>62.5894780096449</v>
+        <v>81.57526055929397</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.5894780096449</v>
+        <v>81.57526055929397</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.8218593123340648</v>
+        <v>0.7678224283909009</v>
       </c>
       <c r="BV10" t="n">
-        <v>478.1294739918604</v>
+        <v>512.8638566041225</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0.3608407674711187</v>
+        <v>-0.459700943349987</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46070.57788194445</v>
+        <v>46071.61920138889</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>02-17_13-52-09_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-18_14-51-39_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3356,7 +3322,7 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AF11" t="n">
         <v>180</v>
@@ -3368,37 +3334,37 @@
         <v>120</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.07841280832210167</v>
+        <v>0.1562368989786031</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.30326020932516</v>
+        <v>13.98551606817886</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.7588765602992997</v>
+        <v>0.6336231635432092</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.1652097057624673</v>
+        <v>-0.03809966766236125</v>
       </c>
       <c r="AM11" t="n">
-        <v>19.81244607758672</v>
+        <v>17.91040204370468</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.7315253102940875</v>
+        <v>0.6289463694077818</v>
       </c>
       <c r="AO11" t="n">
-        <v>19.81244607758672</v>
+        <v>17.91040204370468</v>
       </c>
       <c r="AP11" t="n">
-        <v>19.81244607758672</v>
+        <v>17.91040204370468</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.7315253102940875</v>
+        <v>0.6289463694077818</v>
       </c>
       <c r="AR11" t="n">
-        <v>100.070369297588</v>
+        <v>101.3271193976926</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.03790421362807583</v>
+        <v>-0.06346950780017344</v>
       </c>
       <c r="AT11" t="n">
         <v>0.8</v>
@@ -3409,101 +3375,101 @@
         </is>
       </c>
       <c r="AV11" t="n">
-        <v>0.05189016913930554</v>
+        <v>0.09611510700326743</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.6232102802115322</v>
+        <v>0.3020800503082652</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.05189016913930554</v>
+        <v>0.09611510700326743</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.05189016913930554</v>
+        <v>0.09611510700326743</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.6232102802115322</v>
+        <v>0.3020800503082652</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2882782485810348</v>
+        <v>0.1687231622440652</v>
       </c>
       <c r="BB11" t="n">
-        <v>-1.093272816520483</v>
+        <v>-0.2251483099447134</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.04881799301596813</v>
+        <v>0.0637656406811897</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.8308560808447834</v>
+        <v>0.7790656742334361</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.04881799301596813</v>
+        <v>0.0637656406811897</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.04881799301596813</v>
+        <v>0.0637656406811897</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.8308560808447834</v>
+        <v>0.7790656742334361</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.1316371098760655</v>
+        <v>0.2793420634291076</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.5439055295980599</v>
+        <v>0.03213941265775822</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.07544993912285598</v>
+        <v>0.09021069470335392</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.697092359381198</v>
+        <v>0.6378325945806058</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.07544993912285598</v>
+        <v>0.09021069470335392</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07544993912285598</v>
+        <v>0.09021069470335392</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.697092359381198</v>
+        <v>0.6378325945806058</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.1157008659102253</v>
+        <v>0.2264710439381997</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.5354976197747245</v>
+        <v>0.09079039181071735</v>
       </c>
       <c r="BQ11" t="n">
-        <v>79.07362620906871</v>
+        <v>71.39151673243063</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.7749425207388381</v>
+        <v>0.7968071585088227</v>
       </c>
       <c r="BS11" t="n">
-        <v>79.07362620906871</v>
+        <v>71.39151673243063</v>
       </c>
       <c r="BT11" t="n">
-        <v>79.07362620906871</v>
+        <v>71.39151673243063</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.7749425207388381</v>
+        <v>0.7968071585088227</v>
       </c>
       <c r="BV11" t="n">
-        <v>399.7458609659857</v>
+        <v>404.6339413211596</v>
       </c>
       <c r="BW11" t="n">
-        <v>-0.1377471873646003</v>
+        <v>-0.1516595257244575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46070.57789351852</v>
+        <v>46072.09028935185</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>02-17_13-52-10_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-19_02-10-01_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3621,7 +3587,7 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AF12" t="n">
         <v>180</v>
@@ -3633,37 +3599,37 @@
         <v>120</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.09280227965994661</v>
+        <v>0.06130180038041518</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12.51167159206346</v>
+        <v>10.20244734579202</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.6589820180200056</v>
+        <v>0.7684045917429339</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.07162353597398696</v>
+        <v>-0.102437866043926</v>
       </c>
       <c r="AM12" t="n">
-        <v>16.16351007497544</v>
+        <v>13.10482166982615</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.6593518583453536</v>
+        <v>0.7669597014519531</v>
       </c>
       <c r="AO12" t="n">
-        <v>16.16351007497544</v>
+        <v>13.10482166982615</v>
       </c>
       <c r="AP12" t="n">
-        <v>16.16351007497544</v>
+        <v>13.10482166982615</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.6593518583453536</v>
+        <v>0.7669597014519531</v>
       </c>
       <c r="AR12" t="n">
-        <v>104.1486578544586</v>
+        <v>94.92832358464977</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.1328863371308326</v>
+        <v>-0.02225880219029636</v>
       </c>
       <c r="AT12" t="n">
         <v>0.8</v>
@@ -3674,105 +3640,105 @@
         </is>
       </c>
       <c r="AV12" t="n">
-        <v>0.08769473298542321</v>
+        <v>0.04172205998629838</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.3632228528722748</v>
+        <v>0.6970438996058859</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08769473298542321</v>
+        <v>0.04172205998629838</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.08769473298542321</v>
+        <v>0.04172205998629838</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.3632228528722748</v>
+        <v>0.6970438996058859</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.1825549824471655</v>
+        <v>0.2300657210899208</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.3255852085892184</v>
+        <v>-0.6705746005506887</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.05372949962233753</v>
+        <v>0.04651022034911738</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.8138387594631705</v>
+        <v>0.8388520202366945</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.05372949962233753</v>
+        <v>0.04651022034911738</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.05372949962233753</v>
+        <v>0.04651022034911738</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.8138387594631705</v>
+        <v>0.8388520202366945</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.2979819342957674</v>
+        <v>0.1919423533830468</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.03244375875411709</v>
+        <v>0.3349607409615413</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0887473382034742</v>
+        <v>0.07954302899375525</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6437075080651744</v>
+        <v>0.6806598982016603</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0887473382034742</v>
+        <v>0.07954302899375525</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0887473382034742</v>
+        <v>0.07954302899375525</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.6437075080651744</v>
+        <v>0.6806598982016603</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.2465658966519075</v>
+        <v>0.1679757675801839</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01011591420537117</v>
+        <v>0.3256304242208146</v>
       </c>
       <c r="BQ12" t="n">
-        <v>64.42386872909071</v>
+        <v>52.25151136997533</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.8166383129807913</v>
+        <v>0.8512829877635747</v>
       </c>
       <c r="BS12" t="n">
-        <v>64.42386872909071</v>
+        <v>52.25151136997533</v>
       </c>
       <c r="BT12" t="n">
-        <v>64.42386872909071</v>
+        <v>52.25151136997533</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.8166383129807913</v>
+        <v>0.8512829877635747</v>
       </c>
       <c r="BV12" t="n">
-        <v>415.8675286044402</v>
+        <v>379.1233104965468</v>
       </c>
       <c r="BW12" t="n">
-        <v>-0.1836322953853666</v>
+        <v>-0.07905177339285929</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46070.57792824074</v>
+        <v>46072.54657407408</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>02-17_13-52-13_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-19_13-07-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3886,7 +3852,7 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AF13" t="n">
         <v>180</v>
@@ -3898,37 +3864,37 @@
         <v>120</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1347568375545677</v>
+        <v>0.05148673409953292</v>
       </c>
       <c r="AJ13" t="n">
-        <v>11.76686420237397</v>
+        <v>9.449275579574186</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.7660653996133888</v>
+        <v>0.7938035377360798</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.1882288337888968</v>
+        <v>0.1554465814949441</v>
       </c>
       <c r="AM13" t="n">
-        <v>14.75736286090336</v>
+        <v>11.82475449565026</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.7620104104450187</v>
+        <v>0.8025182673147015</v>
       </c>
       <c r="AO13" t="n">
-        <v>14.75736286090336</v>
+        <v>11.82475449565026</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.75736286090336</v>
+        <v>11.82475449565026</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.7620104104450187</v>
+        <v>0.8025182673147015</v>
       </c>
       <c r="AR13" t="n">
-        <v>99.07109134337652</v>
+        <v>75.67661558029523</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.08849204210837533</v>
+        <v>0.2279710596745222</v>
       </c>
       <c r="AT13" t="n">
         <v>0.8</v>
@@ -3939,105 +3905,105 @@
         </is>
       </c>
       <c r="AV13" t="n">
-        <v>0.04257556393782738</v>
+        <v>0.04203836789421898</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.6908463573725661</v>
+        <v>0.6947470952213729</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.04257556393782738</v>
+        <v>0.04203836789421898</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04257556393782738</v>
+        <v>0.04203836789421898</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.6908463573725661</v>
+        <v>0.6947470952213729</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2438790580901873</v>
+        <v>0.1055569195038727</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.770877287244605</v>
+        <v>0.2335202836818057</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.04653094631197865</v>
+        <v>0.03396889602954492</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.838780209202073</v>
+        <v>0.8823050304027464</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.04653094631197865</v>
+        <v>0.03396889602954492</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.04653094631197865</v>
+        <v>0.03396889602954492</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.838780209202073</v>
+        <v>0.8823050304027464</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.2104085760252538</v>
+        <v>0.2176906854372958</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.2709792235592584</v>
+        <v>0.2457482697741042</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.07822607755798615</v>
+        <v>0.05797194979608877</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6859470416620255</v>
+        <v>0.7672609582068515</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.07822607755798615</v>
+        <v>0.05797194979608877</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07822607755798615</v>
+        <v>0.05797194979608877</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.6859470416620255</v>
+        <v>0.7672609582068515</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1813303561680824</v>
+        <v>0.1761657539291725</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2720159751222109</v>
+        <v>0.2927502195379079</v>
       </c>
       <c r="BQ13" t="n">
-        <v>58.86211885580557</v>
+        <v>47.16503876888108</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.8324680335434115</v>
+        <v>0.8657599854278344</v>
       </c>
       <c r="BS13" t="n">
-        <v>58.86211885580557</v>
+        <v>47.16503876888108</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.86211885580557</v>
+        <v>47.16503876888108</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.8324680335434115</v>
+        <v>0.8657599854278344</v>
       </c>
       <c r="BV13" t="n">
-        <v>395.6487473832226</v>
+        <v>302.2070489623108</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0.12608607987036</v>
+        <v>0.1398654657042663</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46070.57796296296</v>
+        <v>46072.88011574074</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>02-17_13-52-16_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-19_21-07-22_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4151,7 +4117,7 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AF14" t="n">
         <v>180</v>
@@ -4163,37 +4129,37 @@
         <v>120</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.124712634239408</v>
+        <v>0.05379557427035361</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10.24891702410613</v>
+        <v>12.46139548182554</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.787850224007417</v>
+        <v>0.7677672298409929</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.06087001477968185</v>
+        <v>-0.1836059607377363</v>
       </c>
       <c r="AM14" t="n">
-        <v>12.69550708888744</v>
+        <v>15.24877909957026</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.790151413234965</v>
+        <v>0.7788004666895258</v>
       </c>
       <c r="AO14" t="n">
-        <v>12.69550708888744</v>
+        <v>15.24877909957026</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.69550708888744</v>
+        <v>15.24877909957026</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.790151413234965</v>
+        <v>0.7788004666895258</v>
       </c>
       <c r="AR14" t="n">
-        <v>80.10151529294306</v>
+        <v>116.725190647269</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.1276246851708594</v>
+        <v>-0.1213585897766918</v>
       </c>
       <c r="AT14" t="n">
         <v>0.8</v>
@@ -4204,101 +4170,101 @@
         </is>
       </c>
       <c r="AV14" t="n">
-        <v>0.04485597879043379</v>
+        <v>0.05889710513216969</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.6742875970607948</v>
+        <v>0.5723308652256371</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.04485597879043379</v>
+        <v>0.05889710513216969</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.04485597879043379</v>
+        <v>0.05889710513216969</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.6742875970607948</v>
+        <v>0.5723308652256371</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.1529031040334653</v>
+        <v>0.22863703786205</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.1102742326564587</v>
+        <v>-0.6602005130881727</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.03760378228478881</v>
+        <v>0.03194459767638102</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.8697109258746418</v>
+        <v>0.8893187918427465</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.03760378228478881</v>
+        <v>0.03194459767638102</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.03760378228478881</v>
+        <v>0.03194459767638102</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.8697109258746418</v>
+        <v>0.8893187918427465</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.2100041245098935</v>
+        <v>0.2116274749910569</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.2723805616764139</v>
+        <v>0.2667559989776427</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.05959687030543954</v>
+        <v>0.04314818020475857</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.7607374163272604</v>
+        <v>0.8267737043294835</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.05959687030543954</v>
+        <v>0.04314818020475857</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.05959687030543954</v>
+        <v>0.04314818020475857</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.7607374163272604</v>
+        <v>0.8267737043294835</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.1846306963069071</v>
+        <v>0.1905264198331642</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.258766153368702</v>
+        <v>0.2350966882393618</v>
       </c>
       <c r="BQ14" t="n">
-        <v>50.6399717241691</v>
+        <v>60.86112651526753</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.8558697136771636</v>
+        <v>0.8267785053602374</v>
       </c>
       <c r="BS14" t="n">
-        <v>50.6399717241691</v>
+        <v>60.86112651526753</v>
       </c>
       <c r="BT14" t="n">
-        <v>50.6399717241691</v>
+        <v>60.86112651526753</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.8558697136771636</v>
+        <v>0.8267785053602374</v>
       </c>
       <c r="BV14" t="n">
-        <v>319.8585232469213</v>
+        <v>466.2699716563901</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0896262582947791</v>
+        <v>-0.3270865332355992</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46070.91962962963</v>
+        <v>46073.22239583333</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>02-17_22-04-16_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-20_05-20-15_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4416,7 +4382,7 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AF15" t="n">
         <v>180</v>
@@ -4428,37 +4394,37 @@
         <v>120</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.1422839026489602</v>
+        <v>0.06077096440380483</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14.43607972075677</v>
+        <v>11.33817311638418</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.7391301085486564</v>
+        <v>0.7623512305890843</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.3540292039091948</v>
+        <v>-0.1519728312869062</v>
       </c>
       <c r="AM15" t="n">
-        <v>17.53605798652396</v>
+        <v>19.72182000999509</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.7483259603977086</v>
+        <v>0.7354459665152007</v>
       </c>
       <c r="AO15" t="n">
-        <v>17.53605798652396</v>
+        <v>19.72182000999509</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.53605798652396</v>
+        <v>19.72182000999509</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.7483259603977086</v>
+        <v>0.7354459665152007</v>
       </c>
       <c r="AR15" t="n">
-        <v>121.5809207744965</v>
+        <v>101.5961746525762</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.2063437040655124</v>
+        <v>-0.02749568993772761</v>
       </c>
       <c r="AT15" t="n">
         <v>0.8</v>
@@ -4469,101 +4435,101 @@
         </is>
       </c>
       <c r="AV15" t="n">
-        <v>0.06690506576282984</v>
+        <v>0.05225203037936794</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.5141827170859932</v>
+        <v>0.6205826997371002</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06690506576282984</v>
+        <v>0.05225203037936794</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.06690506576282984</v>
+        <v>0.05225203037936794</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.5141827170859932</v>
+        <v>0.6205826997371002</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.2421736560888115</v>
+        <v>0.2802047824753959</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0.7584938637005421</v>
+        <v>-1.03464901393663</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.03601662974652821</v>
+        <v>0.04735747766328706</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.8752100704324842</v>
+        <v>0.8359164546020174</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.03601662974652821</v>
+        <v>0.04735747766328706</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.03601662974652821</v>
+        <v>0.04735747766328706</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.8752100704324842</v>
+        <v>0.8359164546020174</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.2267518140630561</v>
+        <v>0.1299995415487918</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.2143533943799171</v>
+        <v>0.5495793540969269</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.04903963060016262</v>
+        <v>0.07240365236700293</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.8031213944689186</v>
+        <v>0.7093222371596444</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.04903963060016262</v>
+        <v>0.07240365236700293</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.04903963060016262</v>
+        <v>0.07240365236700293</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.8031213944689186</v>
+        <v>0.7093222371596444</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.2239387950151985</v>
+        <v>0.1170132443258543</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.100956570281409</v>
+        <v>0.530228835543767</v>
       </c>
       <c r="BQ15" t="n">
-        <v>69.99227061998641</v>
+        <v>78.71526687957058</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.8007896596034361</v>
+        <v>0.7759624745620424</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.99227061998641</v>
+        <v>78.71526687957058</v>
       </c>
       <c r="BT15" t="n">
-        <v>69.99227061998641</v>
+        <v>78.71526687957058</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.8007896596034361</v>
+        <v>0.7759624745620424</v>
       </c>
       <c r="BV15" t="n">
-        <v>485.6308188328184</v>
+        <v>405.8574810419528</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.3821909172228333</v>
+        <v>-0.1551419354549735</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46071.25741898148</v>
+        <v>46073.56712962963</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02-18_06-10-41_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-20_13-36-40_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4681,7 +4647,7 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AF16" t="n">
         <v>180</v>
@@ -4693,37 +4659,37 @@
         <v>120</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.1468068008913335</v>
+        <v>0.0751152958282003</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11.89758449108911</v>
+        <v>12.02826176466187</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.7348544171690099</v>
+        <v>0.6680631664041488</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.1824293941514002</v>
+        <v>-0.03476315194741902</v>
       </c>
       <c r="AM16" t="n">
-        <v>20.44376784822072</v>
+        <v>15.54011900217286</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.7074937730035297</v>
+        <v>0.6686272014958384</v>
       </c>
       <c r="AO16" t="n">
-        <v>20.44376784822072</v>
+        <v>15.54011900217286</v>
       </c>
       <c r="AP16" t="n">
-        <v>20.44376784822072</v>
+        <v>15.54011900217286</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.7074937730035297</v>
+        <v>0.6686272014958384</v>
       </c>
       <c r="AR16" t="n">
-        <v>128.3682595232955</v>
+        <v>101.0631639851195</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.2084005890128823</v>
+        <v>-0.1130074513114822</v>
       </c>
       <c r="AT16" t="n">
         <v>0.8</v>
@@ -4734,105 +4700,105 @@
         </is>
       </c>
       <c r="AV16" t="n">
-        <v>0.05135137626833674</v>
+        <v>0.08627293575749966</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.6271226130916072</v>
+        <v>0.3735469390718618</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.05135137626833674</v>
+        <v>0.08627293575749966</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.05135137626833674</v>
+        <v>0.08627293575749966</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.6271226130916072</v>
+        <v>0.3735469390718618</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.3138708149551491</v>
+        <v>0.1811544798261724</v>
       </c>
       <c r="BB16" t="n">
-        <v>-1.279107938523697</v>
+        <v>-0.3154157487689904</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0564611151710727</v>
+        <v>0.05059344040542272</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.8043742950107449</v>
+        <v>0.8247045348439468</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0564611151710727</v>
+        <v>0.05059344040542272</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0564611151710727</v>
+        <v>0.05059344040542272</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.8043742950107449</v>
+        <v>0.8247045348439468</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.1650953338199602</v>
+        <v>0.2920971793446228</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.4279799297072132</v>
+        <v>-0.01205433972619652</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.09199834214943828</v>
+        <v>0.08654700982549689</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6306557555208694</v>
+        <v>0.6525411305346962</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.09199834214943828</v>
+        <v>0.08654700982549689</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.09199834214943828</v>
+        <v>0.08654700982549689</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.6306557555208694</v>
+        <v>0.6525411305346962</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.1302153402852377</v>
+        <v>0.2431136228163594</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.4772265961149423</v>
+        <v>0.02397570169430663</v>
       </c>
       <c r="BQ16" t="n">
-        <v>81.57526055929397</v>
+        <v>61.93706262270291</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.7678224283909009</v>
+        <v>0.8237162015328496</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.57526055929397</v>
+        <v>61.93706262270291</v>
       </c>
       <c r="BT16" t="n">
-        <v>81.57526055929397</v>
+        <v>61.93706262270291</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.7678224283909009</v>
+        <v>0.8237162015328496</v>
       </c>
       <c r="BV16" t="n">
-        <v>512.8638566041225</v>
+        <v>403.5362906584922</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0.459700943349987</v>
+        <v>-0.1485354184450456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46071.61920138889</v>
+        <v>46073.90813657407</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>02-18_14-51-39_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-20_21-47-43_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4938,7 +4904,7 @@
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -4946,7 +4912,7 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AF17" t="n">
         <v>180</v>
@@ -4958,37 +4924,37 @@
         <v>120</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1562368989786031</v>
+        <v>0.07755407194774497</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13.98551606817886</v>
+        <v>10.14755561187519</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.6336231635432092</v>
+        <v>0.7669553148905692</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.03809966766236125</v>
+        <v>-0.1177711282789387</v>
       </c>
       <c r="AM17" t="n">
-        <v>17.91040204370468</v>
+        <v>13.15375838059988</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.6289463694077818</v>
+        <v>0.7643770176882269</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.91040204370468</v>
+        <v>13.15375838059988</v>
       </c>
       <c r="AP17" t="n">
-        <v>17.91040204370468</v>
+        <v>13.15375838059988</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6289463694077818</v>
+        <v>0.7643770176882269</v>
       </c>
       <c r="AR17" t="n">
-        <v>101.3271193976926</v>
+        <v>92.66849586915289</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0.06346950780017344</v>
+        <v>-0.02111244731175432</v>
       </c>
       <c r="AT17" t="n">
         <v>0.8</v>
@@ -4999,101 +4965,101 @@
         </is>
       </c>
       <c r="AV17" t="n">
-        <v>0.09611510700326743</v>
+        <v>0.04205767398502145</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.3020800503082652</v>
+        <v>0.6946069080401721</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.09611510700326743</v>
+        <v>0.04205767398502145</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.09611510700326743</v>
+        <v>0.04205767398502145</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.3020800503082652</v>
+        <v>0.6946069080401721</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.1687231622440652</v>
+        <v>0.2317676675650748</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0.2251483099447134</v>
+        <v>-0.6829329325065292</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0637656406811897</v>
+        <v>0.04764088727821016</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.7790656742334361</v>
+        <v>0.8349345008175042</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0637656406811897</v>
+        <v>0.04764088727821016</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0637656406811897</v>
+        <v>0.04764088727821016</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.7790656742334361</v>
+        <v>0.8349345008175042</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.2793420634291076</v>
+        <v>0.1932261392322709</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.03213941265775822</v>
+        <v>0.3305126971875428</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.09021069470335392</v>
+        <v>0.08039632061480265</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6378325945806058</v>
+        <v>0.6772342022409201</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.09021069470335392</v>
+        <v>0.08039632061480265</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.09021069470335392</v>
+        <v>0.08039632061480265</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.6378325945806058</v>
+        <v>0.6772342022409201</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.2264710439381997</v>
+        <v>0.169058606756133</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.09079039181071735</v>
+        <v>0.321283167433473</v>
       </c>
       <c r="BQ17" t="n">
-        <v>71.39151673243063</v>
+        <v>52.44493864052176</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.7968071585088227</v>
+        <v>0.8507324596543104</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.39151673243063</v>
+        <v>52.44493864052176</v>
       </c>
       <c r="BT17" t="n">
-        <v>71.39151673243063</v>
+        <v>52.44493864052176</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.7968071585088227</v>
+        <v>0.8507324596543104</v>
       </c>
       <c r="BV17" t="n">
-        <v>404.6339413211596</v>
+        <v>370.0799310630561</v>
       </c>
       <c r="BW17" t="n">
-        <v>-0.1516595257244575</v>
+        <v>-0.05331272136149767</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46072.09028935185</v>
+        <v>46074.10229166667</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02-19_02-10-01_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-21_02-27-18_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5203,7 +5169,7 @@
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -5211,7 +5177,7 @@
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AF18" t="n">
         <v>180</v>
@@ -5223,37 +5189,37 @@
         <v>120</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.06130180038041518</v>
+        <v>0.06781339228300409</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10.20244734579202</v>
+        <v>9.773359607606039</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.7684045917429339</v>
+        <v>0.7934941923102841</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.102437866043926</v>
+        <v>0.2650948235466237</v>
       </c>
       <c r="AM18" t="n">
-        <v>13.10482166982615</v>
+        <v>12.1743655348489</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.7669597014519531</v>
+        <v>0.8005262828464723</v>
       </c>
       <c r="AO18" t="n">
-        <v>13.10482166982615</v>
+        <v>12.1743655348489</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.10482166982615</v>
+        <v>12.1743655348489</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.7669597014519531</v>
+        <v>0.8005262828464723</v>
       </c>
       <c r="AR18" t="n">
-        <v>94.92832358464977</v>
+        <v>71.02356144678548</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0.02225880219029636</v>
+        <v>0.285704439448544</v>
       </c>
       <c r="AT18" t="n">
         <v>0.8</v>
@@ -5264,105 +5230,105 @@
         </is>
       </c>
       <c r="AV18" t="n">
-        <v>0.04172205998629838</v>
+        <v>0.04251784428710486</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.6970438996058859</v>
+        <v>0.6912654766659265</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.04172205998629838</v>
+        <v>0.04251784428710486</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.04172205998629838</v>
+        <v>0.04251784428710486</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.6970438996058859</v>
+        <v>0.6912654766659265</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.2300657210899208</v>
+        <v>0.1027892459593717</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0.6705746005506887</v>
+        <v>0.2536171721020162</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.04651022034911738</v>
+        <v>0.03438566844322153</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.8388520202366945</v>
+        <v>0.8808610030044471</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.04651022034911738</v>
+        <v>0.03438566844322153</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.04651022034911738</v>
+        <v>0.03438566844322153</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.8388520202366945</v>
+        <v>0.8808610030044471</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.1919423533830468</v>
+        <v>0.1958844428121256</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.3349607409615413</v>
+        <v>0.3213022430491707</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.07954302899375525</v>
+        <v>0.05773879584079594</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6806598982016603</v>
+        <v>0.768196997590312</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.07954302899375525</v>
+        <v>0.05773879584079594</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.07954302899375525</v>
+        <v>0.05773879584079594</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.6806598982016603</v>
+        <v>0.768196997590312</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.1679757675801839</v>
+        <v>0.1556317842857116</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.3256304242208146</v>
+        <v>0.3751876127226912</v>
       </c>
       <c r="BQ18" t="n">
-        <v>52.25151136997533</v>
+        <v>48.56281983082435</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.8512829877635747</v>
+        <v>0.8617816541252052</v>
       </c>
       <c r="BS18" t="n">
-        <v>52.25151136997533</v>
+        <v>48.56281983082435</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.25151136997533</v>
+        <v>48.56281983082435</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.8512829877635747</v>
+        <v>0.8617816541252052</v>
       </c>
       <c r="BV18" t="n">
-        <v>379.1233104965468</v>
+        <v>283.6399403140853</v>
       </c>
       <c r="BW18" t="n">
-        <v>-0.07905177339285929</v>
+        <v>0.1927107299202954</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46072.54657407408</v>
+        <v>46074.30208333334</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02-19_13-07-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-21_07-15-00_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Final (Last Iteration)</t>
+          <t>Best (Lowest Val Loss)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5468,7 +5434,7 @@
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -5476,7 +5442,7 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AF19" t="n">
         <v>180</v>
@@ -5488,37 +5454,37 @@
         <v>120</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.05148673409953292</v>
+        <v>0.07372700162543401</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.449275579574186</v>
+        <v>12.55471995095623</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.7938035377360798</v>
+        <v>0.7576004541351582</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.1554465814949441</v>
+        <v>-0.1932218709786629</v>
       </c>
       <c r="AM19" t="n">
-        <v>11.82475449565026</v>
+        <v>15.28309337951204</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.8025182673147015</v>
+        <v>0.7716739093263906</v>
       </c>
       <c r="AO19" t="n">
-        <v>11.82475449565026</v>
+        <v>15.28309337951204</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.82475449565026</v>
+        <v>15.28309337951204</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.8025182673147015</v>
+        <v>0.7716739093263906</v>
       </c>
       <c r="AR19" t="n">
-        <v>75.67661558029523</v>
+        <v>113.1342207971175</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.2279710596745222</v>
+        <v>-0.115097403923906</v>
       </c>
       <c r="AT19" t="n">
         <v>0.8</v>
@@ -5529,101 +5495,101 @@
         </is>
       </c>
       <c r="AV19" t="n">
-        <v>0.04203836789421898</v>
+        <v>0.0622724230903881</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.6947470952213729</v>
+        <v>0.5478216927028066</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.04203836789421898</v>
+        <v>0.0622724230903881</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.04203836789421898</v>
+        <v>0.0622724230903881</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.6947470952213729</v>
+        <v>0.5478216927028066</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.1055569195038727</v>
+        <v>0.2337959150945133</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.2335202836818057</v>
+        <v>-0.6976606320102088</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.03396889602954492</v>
+        <v>0.03241163989503338</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.8823050304027464</v>
+        <v>0.8877005903069324</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.03396889602954492</v>
+        <v>0.03241163989503338</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.03396889602954492</v>
+        <v>0.03241163989503338</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.8823050304027464</v>
+        <v>0.8877005903069324</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.2176906854372958</v>
+        <v>0.2037285848818222</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.2457482697741042</v>
+        <v>0.2941239661453083</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.05797194979608877</v>
+        <v>0.04364648888723299</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.7672609582068515</v>
+        <v>0.8247731525853342</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.05797194979608877</v>
+        <v>0.04364648888723299</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.05797194979608877</v>
+        <v>0.04364648888723299</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.7672609582068515</v>
+        <v>0.8247731525853342</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.1761657539291725</v>
+        <v>0.1919565473189368</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.2927502195379079</v>
+        <v>0.2293551787360326</v>
       </c>
       <c r="BQ19" t="n">
-        <v>47.16503876888108</v>
+        <v>60.99404296617551</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.8657599854278344</v>
+        <v>0.8264002017104897</v>
       </c>
       <c r="BS19" t="n">
-        <v>47.16503876888108</v>
+        <v>60.99404296617551</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.16503876888108</v>
+        <v>60.99404296617551</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.8657599854278344</v>
+        <v>0.8264002017104897</v>
       </c>
       <c r="BV19" t="n">
-        <v>302.2070489623108</v>
+        <v>451.9074021411748</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.1398654657042663</v>
+        <v>-0.286208128566751</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46072.88011574074</v>
+        <v>46074.50146990741</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02-19_21-07-22_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-21_12-02-07_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5733,7 +5699,7 @@
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -5741,7 +5707,7 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AF20" t="n">
         <v>180</v>
@@ -5753,37 +5719,37 @@
         <v>120</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.05379557427035361</v>
+        <v>0.08100558797707959</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12.46139548182554</v>
+        <v>11.64796646385975</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.7677672298409929</v>
+        <v>0.7471008955495539</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.1836059607377363</v>
+        <v>-0.1344723065780343</v>
       </c>
       <c r="AM20" t="n">
-        <v>15.24877909957026</v>
+        <v>20.30388314574132</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.7788004666895258</v>
+        <v>0.7198699481810062</v>
       </c>
       <c r="AO20" t="n">
-        <v>15.24877909957026</v>
+        <v>20.30388314574132</v>
       </c>
       <c r="AP20" t="n">
-        <v>15.24877909957026</v>
+        <v>20.30388314574132</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.7788004666895258</v>
+        <v>0.7198699481810062</v>
       </c>
       <c r="AR20" t="n">
-        <v>116.725190647269</v>
+        <v>112.8177732350776</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0.1213585897766918</v>
+        <v>-0.06494576276566913</v>
       </c>
       <c r="AT20" t="n">
         <v>0.8</v>
@@ -5794,105 +5760,105 @@
         </is>
       </c>
       <c r="AV20" t="n">
-        <v>0.05889710513216969</v>
+        <v>0.0546263870485101</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.5723308652256371</v>
+        <v>0.6033418003744059</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.05889710513216969</v>
+        <v>0.0546263870485101</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.05889710513216969</v>
+        <v>0.0546263870485101</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.5723308652256371</v>
+        <v>0.6033418003744059</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.22863703786205</v>
+        <v>0.2760862972395882</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0.6602005130881727</v>
+        <v>-1.004743486094027</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.03194459767638102</v>
+        <v>0.05116038374849134</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.8893187918427465</v>
+        <v>0.8227401972491132</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.03194459767638102</v>
+        <v>0.05116038374849134</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.03194459767638102</v>
+        <v>0.05116038374849134</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.8893187918427465</v>
+        <v>0.8227401972491132</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.2116274749910569</v>
+        <v>0.135923659319365</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.2667559989776427</v>
+        <v>0.5290535513068766</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.04314818020475857</v>
+        <v>0.07870447609219075</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.8267737043294835</v>
+        <v>0.6840264228655617</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.04314818020475857</v>
+        <v>0.07870447609219075</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.04314818020475857</v>
+        <v>0.07870447609219075</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.8267737043294835</v>
+        <v>0.6840264228655617</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.1905264198331642</v>
+        <v>0.1248477003628619</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.2350966882393618</v>
+        <v>0.4987759726085492</v>
       </c>
       <c r="BQ20" t="n">
-        <v>60.86112651526753</v>
+        <v>81.031041336076</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.8267785053602374</v>
+        <v>0.7693713722349464</v>
       </c>
       <c r="BS20" t="n">
-        <v>60.86112651526753</v>
+        <v>81.031041336076</v>
       </c>
       <c r="BT20" t="n">
-        <v>60.86112651526753</v>
+        <v>81.031041336076</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.8267785053602374</v>
+        <v>0.7693713722349464</v>
       </c>
       <c r="BV20" t="n">
-        <v>466.2699716563901</v>
+        <v>450.734235283389</v>
       </c>
       <c r="BW20" t="n">
-        <v>-0.3270865332355992</v>
+        <v>-0.2828690888840644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46073.22239583333</v>
+        <v>46074.69827546296</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>02-20_05-20-15_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-21_16-45-31_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5998,7 +5964,7 @@
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -6006,7 +5972,7 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AF21" t="n">
         <v>180</v>
@@ -6018,37 +5984,37 @@
         <v>120</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.06077096440380483</v>
+        <v>0.09341985973782664</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11.33817311638418</v>
+        <v>12.54205922855598</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.7623512305890843</v>
+        <v>0.655221148698768</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.1519728312869062</v>
+        <v>-0.02878854512167098</v>
       </c>
       <c r="AM21" t="n">
-        <v>19.72182000999509</v>
+        <v>16.1771191333453</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.7354459665152007</v>
+        <v>0.6527103399038117</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.72182000999509</v>
+        <v>16.1771191333453</v>
       </c>
       <c r="AP21" t="n">
-        <v>19.72182000999509</v>
+        <v>16.1771191333453</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.7354459665152007</v>
+        <v>0.6527103399038117</v>
       </c>
       <c r="AR21" t="n">
-        <v>101.5961746525762</v>
+        <v>101.9663216447624</v>
       </c>
       <c r="AS21" t="n">
-        <v>-0.02749568993772761</v>
+        <v>-0.09565350199737505</v>
       </c>
       <c r="AT21" t="n">
         <v>0.8</v>
@@ -6059,101 +6025,101 @@
         </is>
       </c>
       <c r="AV21" t="n">
-        <v>0.05225203037936794</v>
+        <v>0.08997235195475747</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.6205826997371002</v>
+        <v>0.3466843942880204</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.05225203037936794</v>
+        <v>0.08997235195475747</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.05225203037936794</v>
+        <v>0.08997235195475747</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.6205826997371002</v>
+        <v>0.3466843942880204</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.2802047824753959</v>
+        <v>0.1787635488061334</v>
       </c>
       <c r="BB21" t="n">
-        <v>-1.03464901393663</v>
+        <v>-0.2980544981888364</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.04735747766328706</v>
+        <v>0.0580105585151317</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.8359164546020174</v>
+        <v>0.7990058047568055</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.04735747766328706</v>
+        <v>0.0580105585151317</v>
       </c>
       <c r="BF21" t="n">
-        <v>0.04735747766328706</v>
+        <v>0.0580105585151317</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.8359164546020174</v>
+        <v>0.7990058047568055</v>
       </c>
       <c r="BH21" t="n">
-        <v>0.1299995415487918</v>
+        <v>0.2864478108072272</v>
       </c>
       <c r="BI21" t="n">
-        <v>0.5495793540969269</v>
+        <v>0.007519515652386954</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.07240365236700293</v>
+        <v>0.08751558156809157</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.7093222371596444</v>
+        <v>0.6486526213492656</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.07240365236700293</v>
+        <v>0.08751558156809157</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.07240365236700293</v>
+        <v>0.08751558156809157</v>
       </c>
       <c r="BN21" t="n">
-        <v>0.7093222371596444</v>
+        <v>0.6486526213492656</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.1170132443258543</v>
+        <v>0.2324487444892836</v>
       </c>
       <c r="BP21" t="n">
-        <v>0.530228835543767</v>
+        <v>0.06679181485618613</v>
       </c>
       <c r="BQ21" t="n">
-        <v>78.71526687957058</v>
+        <v>64.47297804134308</v>
       </c>
       <c r="BR21" t="n">
-        <v>0.7759624745620424</v>
+        <v>0.8164985392211492</v>
       </c>
       <c r="BS21" t="n">
-        <v>78.71526687957058</v>
+        <v>64.47297804134308</v>
       </c>
       <c r="BT21" t="n">
-        <v>78.71526687957058</v>
+        <v>64.47297804134308</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.7759624745620424</v>
+        <v>0.8164985392211492</v>
       </c>
       <c r="BV21" t="n">
-        <v>405.8574810419528</v>
+        <v>407.1676264749462</v>
       </c>
       <c r="BW21" t="n">
-        <v>-0.1551419354549735</v>
+        <v>-0.1588708403092347</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46073.56712962963</v>
+        <v>46074.87417824074</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>02-20_13-36-40_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-21_20-58-49_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6263,7 +6229,7 @@
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -6271,7 +6237,7 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AF22" t="n">
         <v>180</v>
@@ -6283,37 +6249,37 @@
         <v>120</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.0751152958282003</v>
+        <v>0.07721358841446789</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12.02826176466187</v>
+        <v>10.21871371065128</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.6680631664041488</v>
+        <v>0.7687160329509809</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.03476315194741902</v>
+        <v>-0.1018973670859001</v>
       </c>
       <c r="AM22" t="n">
-        <v>15.54011900217286</v>
+        <v>13.1596080130941</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.6686272014958384</v>
+        <v>0.7663771882418285</v>
       </c>
       <c r="AO22" t="n">
-        <v>15.54011900217286</v>
+        <v>13.1596080130941</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.54011900217286</v>
+        <v>13.1596080130941</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.6686272014958384</v>
+        <v>0.7663771882418285</v>
       </c>
       <c r="AR22" t="n">
-        <v>101.0631639851195</v>
+        <v>93.48149264688436</v>
       </c>
       <c r="AS22" t="n">
-        <v>-0.1130074513114822</v>
+        <v>-0.02793199763982446</v>
       </c>
       <c r="AT22" t="n">
         <v>0.8</v>
@@ -6324,105 +6290,105 @@
         </is>
       </c>
       <c r="AV22" t="n">
-        <v>0.08627293575749966</v>
+        <v>0.04172700099549666</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.3735469390718618</v>
+        <v>0.6970080214905864</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.08627293575749966</v>
+        <v>0.04172700099549666</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.08627293575749966</v>
+        <v>0.04172700099549666</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.3735469390718618</v>
+        <v>0.6970080214905864</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.1811544798261724</v>
+        <v>0.23034682928897</v>
       </c>
       <c r="BB22" t="n">
-        <v>-0.3154157487689904</v>
+        <v>-0.6726158095370316</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.05059344040542272</v>
+        <v>0.04649522148229612</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.8247045348439468</v>
+        <v>0.8389039881067419</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.05059344040542272</v>
+        <v>0.04649522148229612</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.05059344040542272</v>
+        <v>0.04649522148229612</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.8247045348439468</v>
+        <v>0.8389039881067419</v>
       </c>
       <c r="BH22" t="n">
-        <v>0.2920971793446228</v>
+        <v>0.1995844674646073</v>
       </c>
       <c r="BI22" t="n">
-        <v>-0.01205433972619652</v>
+        <v>0.3084824478870268</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.08654700982549689</v>
+        <v>0.0799723553552581</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.6525411305346962</v>
+        <v>0.6789362886569723</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.08654700982549689</v>
+        <v>0.0799723553552581</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.08654700982549689</v>
+        <v>0.0799723553552581</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.6525411305346962</v>
+        <v>0.6789362886569723</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.2431136228163594</v>
+        <v>0.1706347920669472</v>
       </c>
       <c r="BP22" t="n">
-        <v>0.02397570169430663</v>
+        <v>0.3149552819609699</v>
       </c>
       <c r="BQ22" t="n">
-        <v>61.93706262270291</v>
+        <v>52.47023747454335</v>
       </c>
       <c r="BR22" t="n">
-        <v>0.8237162015328496</v>
+        <v>0.8506604547130157</v>
       </c>
       <c r="BS22" t="n">
-        <v>61.93706262270291</v>
+        <v>52.47023747454335</v>
       </c>
       <c r="BT22" t="n">
-        <v>61.93706262270291</v>
+        <v>52.47023747454335</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.8237162015328496</v>
+        <v>0.8506604547130157</v>
       </c>
       <c r="BV22" t="n">
-        <v>403.5362906584922</v>
+        <v>373.325404498717</v>
       </c>
       <c r="BW22" t="n">
-        <v>-0.1485354184450456</v>
+        <v>-0.06254991087026895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46073.90813657407</v>
+        <v>46075.41342592592</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>02-20_21-47-43_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-22_09-55-20_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Final (Last Iteration)</t>
+          <t>Best (Lowest Val Loss)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6528,7 +6494,7 @@
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -6548,37 +6514,37 @@
         <v>120</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.07755407194774497</v>
+        <v>0.0678622501719347</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10.14755561187519</v>
+        <v>9.417682816987437</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.7669553148905692</v>
+        <v>0.7944233171032696</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.1177711282789387</v>
+        <v>0.1889042830644831</v>
       </c>
       <c r="AM23" t="n">
-        <v>13.15375838059988</v>
+        <v>11.82339059118003</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.7643770176882269</v>
+        <v>0.8018825971344028</v>
       </c>
       <c r="AO23" t="n">
-        <v>13.15375838059988</v>
+        <v>11.82339059118003</v>
       </c>
       <c r="AP23" t="n">
-        <v>13.15375838059988</v>
+        <v>11.82339059118003</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.7643770176882269</v>
+        <v>0.8018825971344028</v>
       </c>
       <c r="AR23" t="n">
-        <v>92.66849586915289</v>
+        <v>70.05366663124946</v>
       </c>
       <c r="AS23" t="n">
-        <v>-0.02111244731175432</v>
+        <v>0.2591399597158821</v>
       </c>
       <c r="AT23" t="n">
         <v>0.8</v>
@@ -6589,101 +6555,101 @@
         </is>
       </c>
       <c r="AV23" t="n">
-        <v>0.04205767398502145</v>
+        <v>0.04205698271336322</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.6946069080401721</v>
+        <v>0.6946119275661964</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.04205767398502145</v>
+        <v>0.04205698271336322</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.04205767398502145</v>
+        <v>0.04205698271336322</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.6946069080401721</v>
+        <v>0.6946119275661964</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.2317676675650748</v>
+        <v>0.1040742964568097</v>
       </c>
       <c r="BB23" t="n">
-        <v>-0.6829329325065292</v>
+        <v>0.2442860439736072</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.04764088727821016</v>
+        <v>0.03508643527189962</v>
       </c>
       <c r="BD23" t="n">
-        <v>0.8349345008175042</v>
+        <v>0.8784329956142659</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.04764088727821016</v>
+        <v>0.03508643527189962</v>
       </c>
       <c r="BF23" t="n">
-        <v>0.04764088727821016</v>
+        <v>0.03508643527189962</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.8349345008175042</v>
+        <v>0.8784329956142659</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.1932261392322709</v>
+        <v>0.2092516205173617</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.3305126971875428</v>
+        <v>0.2749878272892207</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.08039632061480265</v>
+        <v>0.05761157618433087</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.6772342022409201</v>
+        <v>0.7687077442711996</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.08039632061480265</v>
+        <v>0.05761157618433087</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.08039632061480265</v>
+        <v>0.05761157618433087</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.6772342022409201</v>
+        <v>0.7687077442711996</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.169058606756133</v>
+        <v>0.1710102845370405</v>
       </c>
       <c r="BP23" t="n">
-        <v>0.321283167433473</v>
+        <v>0.313447798462529</v>
       </c>
       <c r="BQ23" t="n">
-        <v>52.44493864052176</v>
+        <v>47.15880737055036</v>
       </c>
       <c r="BR23" t="n">
-        <v>0.8507324596543104</v>
+        <v>0.8657777210859523</v>
       </c>
       <c r="BS23" t="n">
-        <v>52.44493864052176</v>
+        <v>47.15880737055036</v>
       </c>
       <c r="BT23" t="n">
-        <v>52.44493864052176</v>
+        <v>47.15880737055036</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.8507324596543104</v>
+        <v>0.8657777210859523</v>
       </c>
       <c r="BV23" t="n">
-        <v>370.0799310630561</v>
+        <v>279.7303303234857</v>
       </c>
       <c r="BW23" t="n">
-        <v>-0.05331272136149767</v>
+        <v>0.2038381691381732</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46074.10229166667</v>
+        <v>46075.95019675926</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>02-21_02-27-18_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-22_22-48-17_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6793,7 +6759,7 @@
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -6813,37 +6779,37 @@
         <v>120</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.06781339228300409</v>
+        <v>0.0735853188709458</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.773359607606039</v>
+        <v>12.60136472600751</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.7934941923102841</v>
+        <v>0.7628800897288672</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.2650948235466237</v>
+        <v>-0.2346253602248935</v>
       </c>
       <c r="AM24" t="n">
-        <v>12.1743655348489</v>
+        <v>15.39126715769057</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.8005262828464723</v>
+        <v>0.7731678802293929</v>
       </c>
       <c r="AO24" t="n">
-        <v>12.1743655348489</v>
+        <v>15.39126715769057</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.1743655348489</v>
+        <v>15.39126715769057</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.8005262828464723</v>
+        <v>0.7731678802293929</v>
       </c>
       <c r="AR24" t="n">
-        <v>71.02356144678548</v>
+        <v>116.6315926860935</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.285704439448544</v>
+        <v>-0.1373813533864136</v>
       </c>
       <c r="AT24" t="n">
         <v>0.8</v>
@@ -6854,105 +6820,105 @@
         </is>
       </c>
       <c r="AV24" t="n">
-        <v>0.04251784428710486</v>
+        <v>0.06029611115494198</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.6912654766659265</v>
+        <v>0.5621722726435316</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.04251784428710486</v>
+        <v>0.06029611115494198</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.04251784428710486</v>
+        <v>0.06029611115494198</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.6912654766659265</v>
+        <v>0.5621722726435316</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.1027892459593717</v>
+        <v>0.2315543879366423</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.2536171721020162</v>
+        <v>-0.6813842466423932</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.03438566844322153</v>
+        <v>0.0328937200133973</v>
       </c>
       <c r="BD24" t="n">
-        <v>0.8808610030044471</v>
+        <v>0.8860302856604424</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.03438566844322153</v>
+        <v>0.0328937200133973</v>
       </c>
       <c r="BF24" t="n">
-        <v>0.03438566844322153</v>
+        <v>0.0328937200133973</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.8808610030044471</v>
+        <v>0.8860302856604424</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.1958844428121256</v>
+        <v>0.2132870825918027</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.3213022430491707</v>
+        <v>0.2610058131033871</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.05773879584079594</v>
+        <v>0.04500960796651142</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.768196997590312</v>
+        <v>0.8193006606391926</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.05773879584079594</v>
+        <v>0.04500960796651142</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.05773879584079594</v>
+        <v>0.04500960796651142</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.768196997590312</v>
+        <v>0.8193006606391926</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.1556317842857116</v>
+        <v>0.2000571515286874</v>
       </c>
       <c r="BP24" t="n">
-        <v>0.3751876127226912</v>
+        <v>0.1968338150704259</v>
       </c>
       <c r="BQ24" t="n">
-        <v>48.56281983082435</v>
+        <v>61.42686919162728</v>
       </c>
       <c r="BR24" t="n">
-        <v>0.8617816541252052</v>
+        <v>0.8251683019744038</v>
       </c>
       <c r="BS24" t="n">
-        <v>48.56281983082435</v>
+        <v>61.42686919162728</v>
       </c>
       <c r="BT24" t="n">
-        <v>48.56281983082435</v>
+        <v>61.42686919162728</v>
       </c>
       <c r="BU24" t="n">
-        <v>0.8617816541252052</v>
+        <v>0.8251683019744038</v>
       </c>
       <c r="BV24" t="n">
-        <v>283.6399403140853</v>
+        <v>465.881472122315</v>
       </c>
       <c r="BW24" t="n">
-        <v>0.1927107299202954</v>
+        <v>-0.3259807950770646</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46074.30208333334</v>
+        <v>46076.47920138889</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>02-21_07-15-00_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-23_11-30-03_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7058,7 +7024,7 @@
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -7078,37 +7044,37 @@
         <v>120</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.07372700162543401</v>
+        <v>0.07792429729470735</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12.55471995095623</v>
+        <v>11.21950608371635</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.7576004541351582</v>
+        <v>0.7611815029345742</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.1932218709786629</v>
+        <v>-0.1811531247261489</v>
       </c>
       <c r="AM25" t="n">
-        <v>15.28309337951204</v>
+        <v>19.72966568443251</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.7716739093263906</v>
+        <v>0.7337922216933227</v>
       </c>
       <c r="AO25" t="n">
-        <v>15.28309337951204</v>
+        <v>19.72966568443251</v>
       </c>
       <c r="AP25" t="n">
-        <v>15.28309337951204</v>
+        <v>19.72966568443251</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.7716739093263906</v>
+        <v>0.7337922216933227</v>
       </c>
       <c r="AR25" t="n">
-        <v>113.1342207971175</v>
+        <v>94.8193264725865</v>
       </c>
       <c r="AS25" t="n">
-        <v>-0.115097403923906</v>
+        <v>-0.03901374198765545</v>
       </c>
       <c r="AT25" t="n">
         <v>0.8</v>
@@ -7119,101 +7085,101 @@
         </is>
       </c>
       <c r="AV25" t="n">
-        <v>0.0622724230903881</v>
+        <v>0.05126909857705188</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.5478216927028066</v>
+        <v>0.6277200555119786</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.0622724230903881</v>
+        <v>0.05126909857705188</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.0622724230903881</v>
+        <v>0.05126909857705188</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.5478216927028066</v>
+        <v>0.6277200555119786</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.2337959150945133</v>
+        <v>0.2931616249449241</v>
       </c>
       <c r="BB25" t="n">
-        <v>-0.6976606320102088</v>
+        <v>-1.128732442925472</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.03241163989503338</v>
+        <v>0.04851327863789563</v>
       </c>
       <c r="BD25" t="n">
-        <v>0.8877005903069324</v>
+        <v>0.8319118510832949</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.03241163989503338</v>
+        <v>0.04851327863789563</v>
       </c>
       <c r="BF25" t="n">
-        <v>0.03241163989503338</v>
+        <v>0.04851327863789563</v>
       </c>
       <c r="BG25" t="n">
-        <v>0.8877005903069324</v>
+        <v>0.8319118510832949</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.2037285848818222</v>
+        <v>0.1384828066010952</v>
       </c>
       <c r="BI25" t="n">
-        <v>0.2941239661453083</v>
+        <v>0.5201866525635038</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.04364648888723299</v>
+        <v>0.07481125307798775</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.8247731525853342</v>
+        <v>0.6996564818337313</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.04364648888723299</v>
+        <v>0.07481125307798775</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.04364648888723299</v>
+        <v>0.07481125307798775</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.8247731525853342</v>
+        <v>0.6996564818337313</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.1919565473189368</v>
+        <v>0.116965764378399</v>
       </c>
       <c r="BP25" t="n">
-        <v>0.2293551787360326</v>
+        <v>0.5304194525148022</v>
       </c>
       <c r="BQ25" t="n">
-        <v>60.99404296617551</v>
+        <v>78.74406910743707</v>
       </c>
       <c r="BR25" t="n">
-        <v>0.8264002017104897</v>
+        <v>0.775880498344288</v>
       </c>
       <c r="BS25" t="n">
-        <v>60.99404296617551</v>
+        <v>78.74406910743707</v>
       </c>
       <c r="BT25" t="n">
-        <v>60.99404296617551</v>
+        <v>78.74406910743707</v>
       </c>
       <c r="BU25" t="n">
-        <v>0.8264002017104897</v>
+        <v>0.775880498344288</v>
       </c>
       <c r="BV25" t="n">
-        <v>451.9074021411748</v>
+        <v>378.7286956944232</v>
       </c>
       <c r="BW25" t="n">
-        <v>-0.286208128566751</v>
+        <v>-0.07792863010346118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46074.50146990741</v>
+        <v>46077.04608796296</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02-21_12-02-07_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-24_01-06-22_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -7323,7 +7289,7 @@
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -7343,37 +7309,37 @@
         <v>120</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.08100558797707959</v>
+        <v>0.09261835422497917</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11.64796646385975</v>
+        <v>12.60452192043711</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.7471008955495539</v>
+        <v>0.6590060000299733</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.1344723065780343</v>
+        <v>-0.1137097242604768</v>
       </c>
       <c r="AM26" t="n">
-        <v>20.30388314574132</v>
+        <v>16.35383064940526</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.7198699481810062</v>
+        <v>0.6581320289196224</v>
       </c>
       <c r="AO26" t="n">
-        <v>20.30388314574132</v>
+        <v>16.35383064940526</v>
       </c>
       <c r="AP26" t="n">
-        <v>20.30388314574132</v>
+        <v>16.35383064940526</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.7198699481810062</v>
+        <v>0.6581320289196224</v>
       </c>
       <c r="AR26" t="n">
-        <v>112.8177732350776</v>
+        <v>106.4344978103905</v>
       </c>
       <c r="AS26" t="n">
-        <v>-0.06494576276566913</v>
+        <v>-0.1602649184108335</v>
       </c>
       <c r="AT26" t="n">
         <v>0.8</v>
@@ -7384,101 +7350,101 @@
         </is>
       </c>
       <c r="AV26" t="n">
-        <v>0.0546263870485101</v>
+        <v>0.08742189172916187</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.6033418003744059</v>
+        <v>0.3652040331651633</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.0546263870485101</v>
+        <v>0.08742189172916187</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.0546263870485101</v>
+        <v>0.08742189172916187</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.6033418003744059</v>
+        <v>0.3652040331651633</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.2760862972395882</v>
+        <v>0.1831486159295369</v>
       </c>
       <c r="BB26" t="n">
-        <v>-1.004743486094027</v>
+        <v>-0.3298957552147121</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.05116038374849134</v>
+        <v>0.0554840384623443</v>
       </c>
       <c r="BD26" t="n">
-        <v>0.8227401972491132</v>
+        <v>0.8077596571204806</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.05116038374849134</v>
+        <v>0.0554840384623443</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.05116038374849134</v>
+        <v>0.0554840384623443</v>
       </c>
       <c r="BG26" t="n">
-        <v>0.8227401972491132</v>
+        <v>0.8077596571204806</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.135923659319365</v>
+        <v>0.3069162041848398</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.5290535513068766</v>
+        <v>-0.06339909572042446</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.07870447609219075</v>
+        <v>0.0884030743132421</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.6840264228655617</v>
+        <v>0.6450896186931321</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.07870447609219075</v>
+        <v>0.0884030743132421</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.07870447609219075</v>
+        <v>0.0884030743132421</v>
       </c>
       <c r="BN26" t="n">
-        <v>0.6840264228655617</v>
+        <v>0.6450896186931321</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.1248477003628619</v>
+        <v>0.2585932894642791</v>
       </c>
       <c r="BP26" t="n">
-        <v>0.4987759726085492</v>
+        <v>-0.03817026364904397</v>
       </c>
       <c r="BQ26" t="n">
-        <v>81.031041336076</v>
+        <v>65.18401359311663</v>
       </c>
       <c r="BR26" t="n">
-        <v>0.7693713722349464</v>
+        <v>0.8144748066997125</v>
       </c>
       <c r="BS26" t="n">
-        <v>81.031041336076</v>
+        <v>65.18401359311663</v>
       </c>
       <c r="BT26" t="n">
-        <v>81.031041336076</v>
+        <v>65.18401359311663</v>
       </c>
       <c r="BU26" t="n">
-        <v>0.7693713722349464</v>
+        <v>0.8144748066997125</v>
       </c>
       <c r="BV26" t="n">
-        <v>450.734235283389</v>
+        <v>424.9893331319822</v>
       </c>
       <c r="BW26" t="n">
-        <v>-0.2828690888840644</v>
+        <v>-0.2095945590591455</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46074.69827546296</v>
+        <v>46077.58365740741</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02-21_16-45-31_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-24_14-00-28_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -7588,15 +7554,15 @@
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.1, 0.005]</t>
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AF27" t="n">
         <v>180</v>
@@ -7608,37 +7574,37 @@
         <v>120</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09341985973782664</v>
+        <v>0.1448528226900345</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12.54205922855598</v>
+        <v>10.95703117061292</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.655221148698768</v>
+        <v>0.8458639549346482</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.02878854512167098</v>
+        <v>-0.1526893737078079</v>
       </c>
       <c r="AM27" t="n">
-        <v>16.1771191333453</v>
+        <v>14.2735658190605</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.6527103399038117</v>
+        <v>0.836888500907484</v>
       </c>
       <c r="AO27" t="n">
-        <v>16.1771191333453</v>
+        <v>14.2735658190605</v>
       </c>
       <c r="AP27" t="n">
-        <v>16.1771191333453</v>
+        <v>14.2735658190605</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.6527103399038117</v>
+        <v>0.836888500907484</v>
       </c>
       <c r="AR27" t="n">
-        <v>101.9663216447624</v>
+        <v>88.46162720232907</v>
       </c>
       <c r="AS27" t="n">
-        <v>-0.09565350199737505</v>
+        <v>-0.09703028523041735</v>
       </c>
       <c r="AT27" t="n">
         <v>0.8</v>
@@ -7649,101 +7615,101 @@
         </is>
       </c>
       <c r="AV27" t="n">
-        <v>0.08997235195475747</v>
+        <v>0.03476573768456161</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.3466843942880204</v>
+        <v>0.7475557937527922</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.08997235195475747</v>
+        <v>0.03476573768456161</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.08997235195475747</v>
+        <v>0.03476573768456161</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.3466843942880204</v>
+        <v>0.7475557937527922</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.1787635488061334</v>
+        <v>0.3707209278320571</v>
       </c>
       <c r="BB27" t="n">
-        <v>-0.2980544981888364</v>
+        <v>-1.691913262848751</v>
       </c>
       <c r="BC27" t="n">
-        <v>0.0580105585151317</v>
+        <v>0.03076644368269619</v>
       </c>
       <c r="BD27" t="n">
-        <v>0.7990058047568055</v>
+        <v>0.8934008437983655</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.0580105585151317</v>
+        <v>0.03076644368269619</v>
       </c>
       <c r="BF27" t="n">
-        <v>0.0580105585151317</v>
+        <v>0.03076644368269619</v>
       </c>
       <c r="BG27" t="n">
-        <v>0.7990058047568055</v>
+        <v>0.8934008437983655</v>
       </c>
       <c r="BH27" t="n">
-        <v>0.2864478108072272</v>
+        <v>0.09836612687851302</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.007519515652386954</v>
+        <v>0.6591823796011285</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.08751558156809157</v>
+        <v>0.03267550380800271</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.6486526213492656</v>
+        <v>0.8688181875349652</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.08751558156809157</v>
+        <v>0.03267550380800271</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.08751558156809157</v>
+        <v>0.03267550380800271</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.6486526213492656</v>
+        <v>0.8688181875349652</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.2324487444892836</v>
+        <v>0.08714605719088467</v>
       </c>
       <c r="BP27" t="n">
-        <v>0.06679181485618613</v>
+        <v>0.6501361448424869</v>
       </c>
       <c r="BQ27" t="n">
-        <v>64.47297804134308</v>
+        <v>56.99605559106669</v>
       </c>
       <c r="BR27" t="n">
-        <v>0.8164985392211492</v>
+        <v>0.837779178543814</v>
       </c>
       <c r="BS27" t="n">
-        <v>64.47297804134308</v>
+        <v>56.99605559106669</v>
       </c>
       <c r="BT27" t="n">
-        <v>64.47297804134308</v>
+        <v>56.99605559106669</v>
       </c>
       <c r="BU27" t="n">
-        <v>0.8164985392211492</v>
+        <v>0.837779178543814</v>
       </c>
       <c r="BV27" t="n">
-        <v>407.1676264749462</v>
+        <v>353.290275697415</v>
       </c>
       <c r="BW27" t="n">
-        <v>-0.1588708403092347</v>
+        <v>-0.005526402516524254</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46074.87417824074</v>
+        <v>46077.87194444444</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02-21_20-58-49_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-24_20-55-36_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7853,15 +7819,15 @@
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.1, 0.005]</t>
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AF28" t="n">
         <v>180</v>
@@ -7873,37 +7839,37 @@
         <v>120</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.07721358841446789</v>
+        <v>0.1314101025296535</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10.21871371065128</v>
+        <v>9.833746021756228</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.7687160329509809</v>
+        <v>0.8376453888320092</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.1018973670859001</v>
+        <v>0.2898346321974835</v>
       </c>
       <c r="AM28" t="n">
-        <v>13.1596080130941</v>
+        <v>13.2935930896011</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.7663771882418285</v>
+        <v>0.8240643897384843</v>
       </c>
       <c r="AO28" t="n">
-        <v>13.1596080130941</v>
+        <v>13.2935930896011</v>
       </c>
       <c r="AP28" t="n">
-        <v>13.1596080130941</v>
+        <v>13.2935930896011</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.7663771882418285</v>
+        <v>0.8240643897384843</v>
       </c>
       <c r="AR28" t="n">
-        <v>93.48149264688436</v>
+        <v>88.25124165803815</v>
       </c>
       <c r="AS28" t="n">
-        <v>-0.02793199763982446</v>
+        <v>0.2751537941762993</v>
       </c>
       <c r="AT28" t="n">
         <v>0.8</v>
@@ -7914,101 +7880,101 @@
         </is>
       </c>
       <c r="AV28" t="n">
-        <v>0.04172700099549666</v>
+        <v>0.0395381027779944</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.6970080214905864</v>
+        <v>0.712902252704287</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.04172700099549666</v>
+        <v>0.0395381027779944</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.04172700099549666</v>
+        <v>0.0395381027779944</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.6970080214905864</v>
+        <v>0.712902252704287</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.23034682928897</v>
+        <v>0.0645592205383298</v>
       </c>
       <c r="BB28" t="n">
-        <v>-0.6726158095370316</v>
+        <v>0.53121658649647</v>
       </c>
       <c r="BC28" t="n">
-        <v>0.04649522148229612</v>
+        <v>0.02957873885001991</v>
       </c>
       <c r="BD28" t="n">
-        <v>0.8389039881067419</v>
+        <v>0.8975159873712023</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.04649522148229612</v>
+        <v>0.02957873885001991</v>
       </c>
       <c r="BF28" t="n">
-        <v>0.04649522148229612</v>
+        <v>0.02957873885001991</v>
       </c>
       <c r="BG28" t="n">
-        <v>0.8389039881067419</v>
+        <v>0.8975159873712023</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.1995844674646073</v>
+        <v>0.2243141566916586</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.3084824478870268</v>
+        <v>0.2227993565320462</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.0799723553552581</v>
+        <v>0.04063319156351364</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.6789362886569723</v>
+        <v>0.836870588228384</v>
       </c>
       <c r="BL28" t="n">
-        <v>0.0799723553552581</v>
+        <v>0.04063319156351364</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.0799723553552581</v>
+        <v>0.04063319156351364</v>
       </c>
       <c r="BN28" t="n">
-        <v>0.6789362886569723</v>
+        <v>0.836870588228384</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.1706347920669472</v>
+        <v>0.1618980292005632</v>
       </c>
       <c r="BP28" t="n">
-        <v>0.3149552819609699</v>
+        <v>0.3500306214147649</v>
       </c>
       <c r="BQ28" t="n">
-        <v>52.47023747454335</v>
+        <v>53.06462232521302</v>
       </c>
       <c r="BR28" t="n">
-        <v>0.8506604547130157</v>
+        <v>0.848968730650064</v>
       </c>
       <c r="BS28" t="n">
-        <v>52.47023747454335</v>
+        <v>53.06462232521302</v>
       </c>
       <c r="BT28" t="n">
-        <v>52.47023747454335</v>
+        <v>53.06462232521302</v>
       </c>
       <c r="BU28" t="n">
-        <v>0.8506604547130157</v>
+        <v>0.848968730650064</v>
       </c>
       <c r="BV28" t="n">
-        <v>373.325404498717</v>
+        <v>352.5541952257224</v>
       </c>
       <c r="BW28" t="n">
-        <v>-0.06254991087026895</v>
+        <v>-0.003431387738088265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46075.41342592592</v>
+        <v>46078.12157407407</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02-22_09-55-20_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-25_02-55-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -8118,15 +8084,15 @@
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.1, 0.005]</t>
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AF29" t="n">
         <v>180</v>
@@ -8138,37 +8104,37 @@
         <v>120</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.0678622501719347</v>
+        <v>0.149795616384428</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9.417682816987437</v>
+        <v>7.687404412578482</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.7944233171032696</v>
+        <v>0.7870569943420158</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.1889042830644831</v>
+        <v>-0.1268210950849165</v>
       </c>
       <c r="AM29" t="n">
-        <v>11.82339059118003</v>
+        <v>11.8011894210072</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.8018825971344028</v>
+        <v>0.7906646540913554</v>
       </c>
       <c r="AO29" t="n">
-        <v>11.82339059118003</v>
+        <v>11.8011894210072</v>
       </c>
       <c r="AP29" t="n">
-        <v>11.82339059118003</v>
+        <v>11.8011894210072</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.8018825971344028</v>
+        <v>0.7906646540913554</v>
       </c>
       <c r="AR29" t="n">
-        <v>70.05366663124946</v>
+        <v>116.9543910426883</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.2591399597158821</v>
+        <v>-0.2492777927728377</v>
       </c>
       <c r="AT29" t="n">
         <v>0.8</v>
@@ -8179,105 +8145,105 @@
         </is>
       </c>
       <c r="AV29" t="n">
-        <v>0.04205698271336322</v>
+        <v>0.06120046847690248</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.6946119275661964</v>
+        <v>0.5556054691895796</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.04205698271336322</v>
+        <v>0.06120046847690248</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.04205698271336322</v>
+        <v>0.06120046847690248</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.6946119275661964</v>
+        <v>0.5556054691895796</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.1040742964568097</v>
+        <v>0.2342902053020789</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.2442860439736072</v>
+        <v>-0.7012498180138775</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.03508643527189962</v>
+        <v>0.0303109523925596</v>
       </c>
       <c r="BD29" t="n">
-        <v>0.8784329956142659</v>
+        <v>0.894979023833943</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.03508643527189962</v>
+        <v>0.0303109523925596</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.03508643527189962</v>
+        <v>0.0303109523925596</v>
       </c>
       <c r="BG29" t="n">
-        <v>0.8784329956142659</v>
+        <v>0.894979023833943</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.2092516205173617</v>
+        <v>0.2997829730487387</v>
       </c>
       <c r="BI29" t="n">
-        <v>0.2749878272892207</v>
+        <v>-0.03868397336368412</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.05761157618433087</v>
+        <v>0.03834484119824701</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.7687077442711996</v>
+        <v>0.8460575911353501</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.05761157618433087</v>
+        <v>0.03834484119824701</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.05761157618433087</v>
+        <v>0.03834484119824701</v>
       </c>
       <c r="BN29" t="n">
-        <v>0.7687077442711996</v>
+        <v>0.8460575911353501</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.1710102845370405</v>
+        <v>0.231117583088329</v>
       </c>
       <c r="BP29" t="n">
-        <v>0.313447798462529</v>
+        <v>0.07213600683213239</v>
       </c>
       <c r="BQ29" t="n">
-        <v>47.15880737055036</v>
+        <v>47.074901421961</v>
       </c>
       <c r="BR29" t="n">
-        <v>0.8657777210859523</v>
+        <v>0.8660165322065478</v>
       </c>
       <c r="BS29" t="n">
-        <v>47.15880737055036</v>
+        <v>47.074901421961</v>
       </c>
       <c r="BT29" t="n">
-        <v>47.15880737055036</v>
+        <v>47.074901421961</v>
       </c>
       <c r="BU29" t="n">
-        <v>0.8657777210859523</v>
+        <v>0.8660165322065478</v>
       </c>
       <c r="BV29" t="n">
-        <v>279.7303303234857</v>
+        <v>467.0523734093118</v>
       </c>
       <c r="BW29" t="n">
-        <v>0.2038381691381732</v>
+        <v>-0.3293133865459117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46075.95019675926</v>
+        <v>46078.38025462963</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02-22_22-48-17_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-25_09-07-34_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8383,15 +8349,15 @@
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.1, 0.005]</t>
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AF30" t="n">
         <v>180</v>
@@ -8403,37 +8369,37 @@
         <v>120</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.0735853188709458</v>
+        <v>0.1599936757983428</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12.60136472600751</v>
+        <v>11.05536678262606</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.7628800897288672</v>
+        <v>0.805546488646649</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.2346253602248935</v>
+        <v>-0.2298203257556767</v>
       </c>
       <c r="AM30" t="n">
-        <v>15.39126715769057</v>
+        <v>21.37457063926187</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.7731678802293929</v>
+        <v>0.7686828472473387</v>
       </c>
       <c r="AO30" t="n">
-        <v>15.39126715769057</v>
+        <v>21.37457063926187</v>
       </c>
       <c r="AP30" t="n">
-        <v>15.39126715769057</v>
+        <v>21.37457063926187</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.7731678802293929</v>
+        <v>0.7686828472473387</v>
       </c>
       <c r="AR30" t="n">
-        <v>116.6315926860935</v>
+        <v>152.4663396390922</v>
       </c>
       <c r="AS30" t="n">
-        <v>-0.1373813533864136</v>
+        <v>-0.8437623173870255</v>
       </c>
       <c r="AT30" t="n">
         <v>0.8</v>
@@ -8444,101 +8410,101 @@
         </is>
       </c>
       <c r="AV30" t="n">
-        <v>0.06029611115494198</v>
+        <v>0.03960919706384816</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.5621722726435316</v>
+        <v>0.712386016267025</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.06029611115494198</v>
+        <v>0.03960919706384816</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.06029611115494198</v>
+        <v>0.03960919706384816</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.5621722726435316</v>
+        <v>0.712386016267025</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.2315543879366423</v>
+        <v>0.5757150593452737</v>
       </c>
       <c r="BB30" t="n">
-        <v>-0.6813842466423932</v>
+        <v>-3.18043570654682</v>
       </c>
       <c r="BC30" t="n">
-        <v>0.0328937200133973</v>
+        <v>0.04283500811508925</v>
       </c>
       <c r="BD30" t="n">
-        <v>0.8860302856604424</v>
+        <v>0.8515858456683828</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.0328937200133973</v>
+        <v>0.04283500811508925</v>
       </c>
       <c r="BF30" t="n">
-        <v>0.0328937200133973</v>
+        <v>0.04283500811508925</v>
       </c>
       <c r="BG30" t="n">
-        <v>0.8860302856604424</v>
+        <v>0.8515858456683828</v>
       </c>
       <c r="BH30" t="n">
-        <v>0.2132870825918027</v>
+        <v>0.2177978746911188</v>
       </c>
       <c r="BI30" t="n">
-        <v>0.2610058131033871</v>
+        <v>0.2453768819033038</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.04500960796651142</v>
+        <v>0.06135142277951536</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.8193006606391926</v>
+        <v>0.7536934431121357</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.04500960796651142</v>
+        <v>0.06135142277951536</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.04500960796651142</v>
+        <v>0.06135142277951536</v>
       </c>
       <c r="BN30" t="n">
-        <v>0.8193006606391926</v>
+        <v>0.7536934431121357</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.2000571515286874</v>
+        <v>0.1760950191670847</v>
       </c>
       <c r="BP30" t="n">
-        <v>0.1968338150704259</v>
+        <v>0.2930341972341505</v>
       </c>
       <c r="BQ30" t="n">
-        <v>61.42686919162728</v>
+        <v>85.35448692908875</v>
       </c>
       <c r="BR30" t="n">
-        <v>0.8251683019744038</v>
+        <v>0.757066083941811</v>
       </c>
       <c r="BS30" t="n">
-        <v>61.42686919162728</v>
+        <v>85.35448692908875</v>
       </c>
       <c r="BT30" t="n">
-        <v>61.42686919162728</v>
+        <v>85.35448692908875</v>
       </c>
       <c r="BU30" t="n">
-        <v>0.8251683019744038</v>
+        <v>0.757066083941811</v>
       </c>
       <c r="BV30" t="n">
-        <v>465.881472122315</v>
+        <v>608.8957506031642</v>
       </c>
       <c r="BW30" t="n">
-        <v>-0.3259807950770646</v>
+        <v>-0.7330246421387085</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46076.47920138889</v>
+        <v>46078.68253472223</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02-23_11-30-03_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-25_16-22-51_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -8648,15 +8614,15 @@
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.1, 0.005]</t>
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AF31" t="n">
         <v>180</v>
@@ -8668,37 +8634,37 @@
         <v>120</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.07792429729470735</v>
+        <v>0.1744684459638422</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11.21950608371635</v>
+        <v>9.661972563753439</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.7611815029345742</v>
+        <v>0.7810962067096301</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.1811531247261489</v>
+        <v>-0.01774082933391816</v>
       </c>
       <c r="AM31" t="n">
-        <v>19.72966568443251</v>
+        <v>13.55691380665034</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.7337922216933227</v>
+        <v>0.7602489496917539</v>
       </c>
       <c r="AO31" t="n">
-        <v>19.72966568443251</v>
+        <v>13.55691380665034</v>
       </c>
       <c r="AP31" t="n">
-        <v>19.72966568443251</v>
+        <v>13.55691380665034</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.7337922216933227</v>
+        <v>0.7602489496917539</v>
       </c>
       <c r="AR31" t="n">
-        <v>94.8193264725865</v>
+        <v>96.36156004240965</v>
       </c>
       <c r="AS31" t="n">
-        <v>-0.03901374198765545</v>
+        <v>-0.08856779216057672</v>
       </c>
       <c r="AT31" t="n">
         <v>0.8</v>
@@ -8709,105 +8675,105 @@
         </is>
       </c>
       <c r="AV31" t="n">
-        <v>0.05126909857705188</v>
+        <v>0.0523102369787025</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.6277200555119786</v>
+        <v>0.6201600445672119</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.05126909857705188</v>
+        <v>0.0523102369787025</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.05126909857705188</v>
+        <v>0.0523102369787025</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.6277200555119786</v>
+        <v>0.6201600445672119</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.2931616249449241</v>
+        <v>0.3275206904190897</v>
       </c>
       <c r="BB31" t="n">
-        <v>-1.128732442925472</v>
+        <v>-1.378223683114899</v>
       </c>
       <c r="BC31" t="n">
-        <v>0.04851327863789563</v>
+        <v>0.04873294763979857</v>
       </c>
       <c r="BD31" t="n">
-        <v>0.8319118510832949</v>
+        <v>0.8311507449090484</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.04851327863789563</v>
+        <v>0.04873294763979857</v>
       </c>
       <c r="BF31" t="n">
-        <v>0.04851327863789563</v>
+        <v>0.04873294763979857</v>
       </c>
       <c r="BG31" t="n">
-        <v>0.8319118510832949</v>
+        <v>0.8311507449090484</v>
       </c>
       <c r="BH31" t="n">
-        <v>0.1384828066010952</v>
+        <v>0.1295715685606994</v>
       </c>
       <c r="BI31" t="n">
-        <v>0.5201866525635038</v>
+        <v>0.5510621890933358</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.07481125307798775</v>
+        <v>0.06387624374734133</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.6996564818337313</v>
+        <v>0.743557085531996</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.07481125307798775</v>
+        <v>0.06387624374734133</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.07481125307798775</v>
+        <v>0.06387624374734133</v>
       </c>
       <c r="BN31" t="n">
-        <v>0.6996564818337313</v>
+        <v>0.743557085531996</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.116965764378399</v>
+        <v>0.1075224735732624</v>
       </c>
       <c r="BP31" t="n">
-        <v>0.5304194525148022</v>
+        <v>0.5683312781665562</v>
       </c>
       <c r="BQ31" t="n">
-        <v>78.74406910743707</v>
+        <v>54.06273579823565</v>
       </c>
       <c r="BR31" t="n">
-        <v>0.775880498344288</v>
+        <v>0.8461279237587604</v>
       </c>
       <c r="BS31" t="n">
-        <v>78.74406910743707</v>
+        <v>54.06273579823565</v>
       </c>
       <c r="BT31" t="n">
-        <v>78.74406910743707</v>
+        <v>54.06273579823565</v>
       </c>
       <c r="BU31" t="n">
-        <v>0.775880498344288</v>
+        <v>0.8461279237587604</v>
       </c>
       <c r="BV31" t="n">
-        <v>378.7286956944232</v>
+        <v>384.8816254370847</v>
       </c>
       <c r="BW31" t="n">
-        <v>-0.07792863010346118</v>
+        <v>-0.09544095278729969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46077.04608796296</v>
+        <v>46078.97717592592</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>02-24_01-06-22_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-25_23-27-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Final (Last Iteration)</t>
+          <t>Best (Lowest Val Loss)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -8917,11 +8883,11 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>[0.05, 0.001]</t>
+          <t>[0.01, 0.0005]</t>
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AF32" t="n">
         <v>180</v>
@@ -8933,37 +8899,37 @@
         <v>120</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.09261835422497917</v>
+        <v>0.1591133164993049</v>
       </c>
       <c r="AJ32" t="n">
-        <v>12.60452192043711</v>
+        <v>23.76731130572179</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.6590060000299733</v>
+        <v>0.3623696602491133</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.1137097242604768</v>
+        <v>-0.2203559043159494</v>
       </c>
       <c r="AM32" t="n">
-        <v>16.35383064940526</v>
+        <v>26.80419074319915</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.6581320289196224</v>
+        <v>0.4078973530980483</v>
       </c>
       <c r="AO32" t="n">
-        <v>16.35383064940526</v>
+        <v>26.80419074319915</v>
       </c>
       <c r="AP32" t="n">
-        <v>16.35383064940526</v>
+        <v>26.80419074319915</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.6581320289196224</v>
+        <v>0.4078973530980483</v>
       </c>
       <c r="AR32" t="n">
-        <v>106.4344978103905</v>
+        <v>107.7487677249886</v>
       </c>
       <c r="AS32" t="n">
-        <v>-0.1602649184108335</v>
+        <v>-0.1920405892999608</v>
       </c>
       <c r="AT32" t="n">
         <v>0.8</v>
@@ -8974,101 +8940,101 @@
         </is>
       </c>
       <c r="AV32" t="n">
-        <v>0.08742189172916187</v>
+        <v>0.1084906814355005</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.3652040331651633</v>
+        <v>0.2122173788256562</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.08742189172916187</v>
+        <v>0.1084906814355005</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.08742189172916187</v>
+        <v>0.1084906814355005</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.3652040331651633</v>
+        <v>0.2122173788256562</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.1831486159295369</v>
+        <v>0.1915399417630574</v>
       </c>
       <c r="BB32" t="n">
-        <v>-0.3298957552147121</v>
+        <v>-0.3908276304024336</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.0554840384623443</v>
+        <v>0.1317838071242491</v>
       </c>
       <c r="BD32" t="n">
-        <v>0.8077596571204806</v>
+        <v>0.5433972549649968</v>
       </c>
       <c r="BE32" t="n">
-        <v>0.0554840384623443</v>
+        <v>0.1317838071242491</v>
       </c>
       <c r="BF32" t="n">
-        <v>0.0554840384623443</v>
+        <v>0.1317838071242491</v>
       </c>
       <c r="BG32" t="n">
-        <v>0.8077596571204806</v>
+        <v>0.5433972549649968</v>
       </c>
       <c r="BH32" t="n">
-        <v>0.3069162041848398</v>
+        <v>0.3059189854267712</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.06339909572042446</v>
+        <v>-0.05994394571170436</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.0884030743132421</v>
+        <v>0.2042832674402151</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.6450896186931321</v>
+        <v>0.1798672964141548</v>
       </c>
       <c r="BL32" t="n">
-        <v>0.0884030743132421</v>
+        <v>0.2042832674402151</v>
       </c>
       <c r="BM32" t="n">
-        <v>0.0884030743132421</v>
+        <v>0.2042832674402151</v>
       </c>
       <c r="BN32" t="n">
-        <v>0.6450896186931321</v>
+        <v>0.1798672964141548</v>
       </c>
       <c r="BO32" t="n">
-        <v>0.2585932894642791</v>
+        <v>0.2722240578063271</v>
       </c>
       <c r="BP32" t="n">
-        <v>-0.03817026364904397</v>
+        <v>-0.09289348710437562</v>
       </c>
       <c r="BQ32" t="n">
-        <v>65.18401359311663</v>
+        <v>106.7722052167969</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.8144748066997125</v>
+        <v>0.6961074821873809</v>
       </c>
       <c r="BS32" t="n">
-        <v>65.18401359311663</v>
+        <v>106.7722052167969</v>
       </c>
       <c r="BT32" t="n">
-        <v>65.18401359311663</v>
+        <v>106.7722052167969</v>
       </c>
       <c r="BU32" t="n">
-        <v>0.8144748066997125</v>
+        <v>0.6961074821873809</v>
       </c>
       <c r="BV32" t="n">
-        <v>424.9893331319822</v>
+        <v>430.2253879149575</v>
       </c>
       <c r="BW32" t="n">
-        <v>-0.2095945590591455</v>
+        <v>-0.2244972939813314</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46077.58365740741</v>
+        <v>46079.68121527778</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02-24_14-00-28_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-26_16-20-57_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9178,15 +9144,15 @@
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>[0.1, 0.005]</t>
+          <t>[0.01, 0.0005]</t>
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="AF33" t="n">
         <v>180</v>
@@ -9198,37 +9164,37 @@
         <v>120</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.1448528226900345</v>
+        <v>0.1535401410543428</v>
       </c>
       <c r="AJ33" t="n">
-        <v>10.95703117061292</v>
+        <v>28.63624293399343</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.8458639549346482</v>
+        <v>0.3673070524240782</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.1526893737078079</v>
+        <v>-0.1850266394329405</v>
       </c>
       <c r="AM33" t="n">
-        <v>14.2735658190605</v>
+        <v>32.44398207201748</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.836888500907484</v>
+        <v>0.4132439460318347</v>
       </c>
       <c r="AO33" t="n">
-        <v>14.2735658190605</v>
+        <v>32.44398207201748</v>
       </c>
       <c r="AP33" t="n">
-        <v>14.2735658190605</v>
+        <v>32.44398207201748</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.836888500907484</v>
+        <v>0.4132439460318347</v>
       </c>
       <c r="AR33" t="n">
-        <v>88.46162720232907</v>
+        <v>92.76904123264814</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.09703028523041735</v>
+        <v>-0.1310563136572235</v>
       </c>
       <c r="AT33" t="n">
         <v>0.8</v>
@@ -9239,105 +9205,105 @@
         </is>
       </c>
       <c r="AV33" t="n">
-        <v>0.03476573768456161</v>
+        <v>0.1104287051895017</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.7475557937527922</v>
+        <v>0.1981448205872527</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.03476573768456161</v>
+        <v>0.1104287051895017</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.03476573768456161</v>
+        <v>0.1104287051895017</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.7475557937527922</v>
+        <v>0.1981448205872527</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.3707209278320571</v>
+        <v>0.1668428776538589</v>
       </c>
       <c r="BB33" t="n">
-        <v>-1.691913262848751</v>
+        <v>-0.2114950126898054</v>
       </c>
       <c r="BC33" t="n">
-        <v>0.03076644368269619</v>
+        <v>0.1041841981164686</v>
       </c>
       <c r="BD33" t="n">
-        <v>0.8934008437983655</v>
+        <v>0.6390240053969665</v>
       </c>
       <c r="BE33" t="n">
-        <v>0.03076644368269619</v>
+        <v>0.1041841981164686</v>
       </c>
       <c r="BF33" t="n">
-        <v>0.03076644368269619</v>
+        <v>0.1041841981164686</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.8934008437983655</v>
+        <v>0.6390240053969665</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.09836612687851302</v>
+        <v>0.3220556819463247</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.6591823796011285</v>
+        <v>-0.1158541526438668</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.03267550380800271</v>
+        <v>0.2032581565968143</v>
       </c>
       <c r="BK33" t="n">
-        <v>0.8688181875349652</v>
+        <v>0.1839827922058968</v>
       </c>
       <c r="BL33" t="n">
-        <v>0.03267550380800271</v>
+        <v>0.2032581565968143</v>
       </c>
       <c r="BM33" t="n">
-        <v>0.03267550380800271</v>
+        <v>0.2032581565968143</v>
       </c>
       <c r="BN33" t="n">
-        <v>0.8688181875349652</v>
+        <v>0.1839827922058968</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.08714605719088467</v>
+        <v>0.2846873523675547</v>
       </c>
       <c r="BP33" t="n">
-        <v>0.6501361448424869</v>
+        <v>-0.142929672603894</v>
       </c>
       <c r="BQ33" t="n">
-        <v>56.99605559106669</v>
+        <v>129.358057228167</v>
       </c>
       <c r="BR33" t="n">
-        <v>0.837779178543814</v>
+        <v>0.6318241659372197</v>
       </c>
       <c r="BS33" t="n">
-        <v>56.99605559106669</v>
+        <v>129.358057228167</v>
       </c>
       <c r="BT33" t="n">
-        <v>56.99605559106669</v>
+        <v>129.358057228167</v>
       </c>
       <c r="BU33" t="n">
-        <v>0.837779178543814</v>
+        <v>0.6318241659372197</v>
       </c>
       <c r="BV33" t="n">
-        <v>353.290275697415</v>
+        <v>370.3025790186248</v>
       </c>
       <c r="BW33" t="n">
-        <v>-0.005526402516524254</v>
+        <v>-0.05394641669134725</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46077.87194444444</v>
+        <v>46080.41226851852</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02-24_20-55-36_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-27_09-53-40_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Final (Last Iteration)</t>
+          <t>Best (Lowest Val Loss)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9443,15 +9409,15 @@
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>[0.1, 0.005]</t>
+          <t>[0.01, 0.0005]</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="AF34" t="n">
         <v>180</v>
@@ -9463,37 +9429,37 @@
         <v>120</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.1314101025296535</v>
+        <v>0.1715666890698261</v>
       </c>
       <c r="AJ34" t="n">
-        <v>9.833746021756228</v>
+        <v>36.02061205145237</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.8376453888320092</v>
+        <v>0.3090805259427145</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.2898346321974835</v>
+        <v>-0.2584687749480485</v>
       </c>
       <c r="AM34" t="n">
-        <v>13.2935930896011</v>
+        <v>41.81971603165299</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.8240643897384843</v>
+        <v>0.3696429256980438</v>
       </c>
       <c r="AO34" t="n">
-        <v>13.2935930896011</v>
+        <v>41.81971603165299</v>
       </c>
       <c r="AP34" t="n">
-        <v>13.2935930896011</v>
+        <v>41.81971603165299</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.8240643897384843</v>
+        <v>0.3696429256980438</v>
       </c>
       <c r="AR34" t="n">
-        <v>88.25124165803815</v>
+        <v>120.9420713293517</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.2751537941762993</v>
+        <v>-0.1900459898769881</v>
       </c>
       <c r="AT34" t="n">
         <v>0.8</v>
@@ -9504,105 +9470,105 @@
         </is>
       </c>
       <c r="AV34" t="n">
-        <v>0.0395381027779944</v>
+        <v>0.1190224028029209</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.712902252704287</v>
+        <v>0.1357434646191465</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.0395381027779944</v>
+        <v>0.1190224028029209</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.0395381027779944</v>
+        <v>0.1190224028029209</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.712902252704287</v>
+        <v>0.1357434646191465</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.0645592205383298</v>
+        <v>0.1832126530273929</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.53121658649647</v>
+        <v>-0.3303607473424595</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.02957873885001991</v>
+        <v>0.114906969473966</v>
       </c>
       <c r="BD34" t="n">
-        <v>0.8975159873712023</v>
+        <v>0.6018718928343061</v>
       </c>
       <c r="BE34" t="n">
-        <v>0.02957873885001991</v>
+        <v>0.114906969473966</v>
       </c>
       <c r="BF34" t="n">
-        <v>0.02957873885001991</v>
+        <v>0.114906969473966</v>
       </c>
       <c r="BG34" t="n">
-        <v>0.8975159873712023</v>
+        <v>0.6018718928343061</v>
       </c>
       <c r="BH34" t="n">
-        <v>0.2243141566916586</v>
+        <v>0.2988135299585106</v>
       </c>
       <c r="BI34" t="n">
-        <v>0.2227993565320462</v>
+        <v>-0.03532506011164815</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0.04063319156351364</v>
+        <v>0.1953230457287576</v>
       </c>
       <c r="BK34" t="n">
-        <v>0.836870588228384</v>
+        <v>0.2158397524504617</v>
       </c>
       <c r="BL34" t="n">
-        <v>0.04063319156351364</v>
+        <v>0.1953230457287576</v>
       </c>
       <c r="BM34" t="n">
-        <v>0.04063319156351364</v>
+        <v>0.1953230457287576</v>
       </c>
       <c r="BN34" t="n">
-        <v>0.836870588228384</v>
+        <v>0.2158397524504617</v>
       </c>
       <c r="BO34" t="n">
-        <v>0.1618980292005632</v>
+        <v>0.2539934031450133</v>
       </c>
       <c r="BP34" t="n">
-        <v>0.3500306214147649</v>
+        <v>-0.0197031750299963</v>
       </c>
       <c r="BQ34" t="n">
-        <v>53.06462232521302</v>
+        <v>166.8496117086063</v>
       </c>
       <c r="BR34" t="n">
-        <v>0.848968730650064</v>
+        <v>0.5251165928882618</v>
       </c>
       <c r="BS34" t="n">
-        <v>53.06462232521302</v>
+        <v>166.8496117086063</v>
       </c>
       <c r="BT34" t="n">
-        <v>53.06462232521302</v>
+        <v>166.8496117086063</v>
       </c>
       <c r="BU34" t="n">
-        <v>0.848968730650064</v>
+        <v>0.5251165928882618</v>
       </c>
       <c r="BV34" t="n">
-        <v>352.5541952257224</v>
+        <v>483.0322657312786</v>
       </c>
       <c r="BW34" t="n">
-        <v>-0.003431387738088265</v>
+        <v>-0.3747949770238526</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46078.12157407407</v>
+        <v>46081.16131944444</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02-25_02-55-04_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-28_03-52-18_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Best (Lowest Val Loss)</t>
+          <t>Final (Last Iteration)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -9708,15 +9674,15 @@
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>[0.1, 0.005]</t>
+          <t>[0.01, 0.0005]</t>
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="AF35" t="n">
         <v>180</v>
@@ -9728,37 +9694,37 @@
         <v>120</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.149795616384428</v>
+        <v>0.1573693210777558</v>
       </c>
       <c r="AJ35" t="n">
-        <v>7.687404412578482</v>
+        <v>35.38953797425802</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.7870569943420158</v>
+        <v>0.3639791246836664</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.1268210950849165</v>
+        <v>-0.1168826118850578</v>
       </c>
       <c r="AM35" t="n">
-        <v>11.8011894210072</v>
+        <v>41.31839929210679</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.7906646540913554</v>
+        <v>0.3889552642318928</v>
       </c>
       <c r="AO35" t="n">
-        <v>11.8011894210072</v>
+        <v>41.31839929210679</v>
       </c>
       <c r="AP35" t="n">
-        <v>11.8011894210072</v>
+        <v>41.31839929210679</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.7906646540913554</v>
+        <v>0.3889552642318928</v>
       </c>
       <c r="AR35" t="n">
-        <v>116.9543910426883</v>
+        <v>92.14000860948107</v>
       </c>
       <c r="AS35" t="n">
-        <v>-0.2492777927728377</v>
+        <v>-0.092217284179748</v>
       </c>
       <c r="AT35" t="n">
         <v>0.8</v>
@@ -9769,101 +9735,101 @@
         </is>
       </c>
       <c r="AV35" t="n">
-        <v>0.06120046847690248</v>
+        <v>0.1104683641262378</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.5556054691895796</v>
+        <v>0.1978568454291879</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.06120046847690248</v>
+        <v>0.1104683641262378</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.06120046847690248</v>
+        <v>0.1104683641262378</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.5556054691895796</v>
+        <v>0.1978568454291879</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.2342902053020789</v>
+        <v>0.1710613093026648</v>
       </c>
       <c r="BB35" t="n">
-        <v>-0.7012498180138775</v>
+        <v>-0.2421262807173439</v>
       </c>
       <c r="BC35" t="n">
-        <v>0.0303109523925596</v>
+        <v>0.1327887969808059</v>
       </c>
       <c r="BD35" t="n">
-        <v>0.894979023833943</v>
+        <v>0.5399151797597821</v>
       </c>
       <c r="BE35" t="n">
-        <v>0.0303109523925596</v>
+        <v>0.1327887969808059</v>
       </c>
       <c r="BF35" t="n">
-        <v>0.0303109523925596</v>
+        <v>0.1327887969808059</v>
       </c>
       <c r="BG35" t="n">
-        <v>0.894979023833943</v>
+        <v>0.5399151797597821</v>
       </c>
       <c r="BH35" t="n">
-        <v>0.2997829730487387</v>
+        <v>0.3070016729375435</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.03868397336368412</v>
+        <v>-0.063695226693955</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.03834484119824701</v>
+        <v>0.1775359857519239</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.8460575911353501</v>
+        <v>0.2872491721764966</v>
       </c>
       <c r="BL35" t="n">
-        <v>0.03834484119824701</v>
+        <v>0.1775359857519239</v>
       </c>
       <c r="BM35" t="n">
-        <v>0.03834484119824701</v>
+        <v>0.1775359857519239</v>
       </c>
       <c r="BN35" t="n">
-        <v>0.8460575911353501</v>
+        <v>0.2872491721764966</v>
       </c>
       <c r="BO35" t="n">
-        <v>0.231117583088329</v>
+        <v>0.2531063253849958</v>
       </c>
       <c r="BP35" t="n">
-        <v>0.07213600683213239</v>
+        <v>-0.01614183840791128</v>
       </c>
       <c r="BQ35" t="n">
-        <v>47.074901421961</v>
+        <v>164.8528040215678</v>
       </c>
       <c r="BR35" t="n">
-        <v>0.8660165322065478</v>
+        <v>0.5307998595621081</v>
       </c>
       <c r="BS35" t="n">
-        <v>47.074901421961</v>
+        <v>164.8528040215678</v>
       </c>
       <c r="BT35" t="n">
-        <v>47.074901421961</v>
+        <v>164.8528040215678</v>
       </c>
       <c r="BU35" t="n">
-        <v>0.8660165322065478</v>
+        <v>0.5307998595621081</v>
       </c>
       <c r="BV35" t="n">
-        <v>467.0523734093118</v>
+        <v>367.8288651302984</v>
       </c>
       <c r="BW35" t="n">
-        <v>-0.3293133865459117</v>
+        <v>-0.04690579089978297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46078.38025462963</v>
+        <v>46081.66032407407</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02-25_09-07-34_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>02-28_15-50-52_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9973,15 +9939,15 @@
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>[0.1, 0.005]</t>
+          <t>[0.01, 0.0005]</t>
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="AF36" t="n">
         <v>180</v>
@@ -9993,37 +9959,37 @@
         <v>120</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.1599936757983428</v>
+        <v>0.1644362116238827</v>
       </c>
       <c r="AJ36" t="n">
-        <v>11.05536678262606</v>
+        <v>36.18299408594576</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.805546488646649</v>
+        <v>0.3018063693832541</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.2298203257556767</v>
+        <v>-0.226263341426982</v>
       </c>
       <c r="AM36" t="n">
-        <v>21.37457063926187</v>
+        <v>41.44500022863073</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.7686828472473387</v>
+        <v>0.3183389441492139</v>
       </c>
       <c r="AO36" t="n">
-        <v>21.37457063926187</v>
+        <v>41.44500022863073</v>
       </c>
       <c r="AP36" t="n">
-        <v>21.37457063926187</v>
+        <v>41.44500022863073</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.7686828472473387</v>
+        <v>0.3183389441492139</v>
       </c>
       <c r="AR36" t="n">
-        <v>152.4663396390922</v>
+        <v>118.3998759230345</v>
       </c>
       <c r="AS36" t="n">
-        <v>-0.8437623173870255</v>
+        <v>-0.167187080994926</v>
       </c>
       <c r="AT36" t="n">
         <v>0.8</v>
@@ -10034,101 +10000,101 @@
         </is>
       </c>
       <c r="AV36" t="n">
-        <v>0.03960919706384816</v>
+        <v>0.150336632874505</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.712386016267025</v>
+        <v>-0.09163833370161534</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.03960919706384816</v>
+        <v>0.150336632874505</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.03960919706384816</v>
+        <v>0.150336632874505</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.712386016267025</v>
+        <v>-0.09163833370161534</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.5757150593452737</v>
+        <v>0.1574461954827236</v>
       </c>
       <c r="BB36" t="n">
-        <v>-3.18043570654682</v>
+        <v>-0.1432629506069421</v>
       </c>
       <c r="BC36" t="n">
-        <v>0.04283500811508925</v>
+        <v>0.1331502148711081</v>
       </c>
       <c r="BD36" t="n">
-        <v>0.8515858456683828</v>
+        <v>0.5386629439622447</v>
       </c>
       <c r="BE36" t="n">
-        <v>0.04283500811508925</v>
+        <v>0.1331502148711081</v>
       </c>
       <c r="BF36" t="n">
-        <v>0.04283500811508925</v>
+        <v>0.1331502148711081</v>
       </c>
       <c r="BG36" t="n">
-        <v>0.8515858456683828</v>
+        <v>0.5386629439622447</v>
       </c>
       <c r="BH36" t="n">
-        <v>0.2177978746911188</v>
+        <v>0.3277769036277456</v>
       </c>
       <c r="BI36" t="n">
-        <v>0.2453768819033038</v>
+        <v>-0.1356769638199589</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06135142277951536</v>
+        <v>0.1751408368717478</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.7536934431121357</v>
+        <v>0.2968649373402505</v>
       </c>
       <c r="BL36" t="n">
-        <v>0.06135142277951536</v>
+        <v>0.1751408368717478</v>
       </c>
       <c r="BM36" t="n">
-        <v>0.06135142277951536</v>
+        <v>0.1751408368717478</v>
       </c>
       <c r="BN36" t="n">
-        <v>0.7536934431121357</v>
+        <v>0.2968649373402505</v>
       </c>
       <c r="BO36" t="n">
-        <v>0.1760950191670847</v>
+        <v>0.2600408817401755</v>
       </c>
       <c r="BP36" t="n">
-        <v>0.2930341972341505</v>
+        <v>-0.04398188876057341</v>
       </c>
       <c r="BQ36" t="n">
-        <v>85.35448692908875</v>
+        <v>165.3213732299057</v>
       </c>
       <c r="BR36" t="n">
-        <v>0.757066083941811</v>
+        <v>0.5294662289959684</v>
       </c>
       <c r="BS36" t="n">
-        <v>85.35448692908875</v>
+        <v>165.3213732299057</v>
       </c>
       <c r="BT36" t="n">
-        <v>85.35448692908875</v>
+        <v>165.3213732299057</v>
       </c>
       <c r="BU36" t="n">
-        <v>0.757066083941811</v>
+        <v>0.5294662289959684</v>
       </c>
       <c r="BV36" t="n">
-        <v>608.8957506031642</v>
+        <v>472.8542397112872</v>
       </c>
       <c r="BW36" t="n">
-        <v>-0.7330246421387085</v>
+        <v>-0.3458265207922213</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46078.68253472223</v>
+        <v>46082.09128472222</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>02-25_16-22-51_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+          <t>03-01_02-11-27_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10242,11 +10208,11 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>[0.1, 0.005]</t>
+          <t>[0.1, 0.001]</t>
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AF37" t="n">
         <v>180</v>
@@ -10258,37 +10224,37 @@
         <v>120</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.1744684459638422</v>
+        <v>0.07407991010031648</v>
       </c>
       <c r="AJ37" t="n">
-        <v>9.661972563753439</v>
+        <v>10.18341462504053</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.7810962067096301</v>
+        <v>0.8558148424092853</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.01774082933391816</v>
+        <v>0.2600452677688797</v>
       </c>
       <c r="AM37" t="n">
-        <v>13.55691380665034</v>
+        <v>13.74494545115664</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.7602489496917539</v>
+        <v>0.8519430722610524</v>
       </c>
       <c r="AO37" t="n">
-        <v>13.55691380665034</v>
+        <v>13.74494545115664</v>
       </c>
       <c r="AP37" t="n">
-        <v>13.55691380665034</v>
+        <v>13.74494545115664</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.7602489496917539</v>
+        <v>0.8519430722610524</v>
       </c>
       <c r="AR37" t="n">
-        <v>96.36156004240965</v>
+        <v>94.70533781186118</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.08856779216057672</v>
+        <v>0.08567925055765599</v>
       </c>
       <c r="AT37" t="n">
         <v>0.8</v>
@@ -10299,618 +10265,88 @@
         </is>
       </c>
       <c r="AV37" t="n">
-        <v>0.0523102369787025</v>
+        <v>0.03085790525152717</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.6201600445672119</v>
+        <v>0.7759317098819228</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.0523102369787025</v>
+        <v>0.03085790525152717</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.0523102369787025</v>
+        <v>0.03085790525152717</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.6201600445672119</v>
+        <v>0.7759317098819228</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.3275206904190897</v>
+        <v>0.2548581314754902</v>
       </c>
       <c r="BB37" t="n">
-        <v>-1.378223683114899</v>
+        <v>-0.8505995555085524</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.04873294763979857</v>
+        <v>0.02717693426506614</v>
       </c>
       <c r="BD37" t="n">
-        <v>0.8311507449090484</v>
+        <v>0.9058377272758142</v>
       </c>
       <c r="BE37" t="n">
-        <v>0.04873294763979857</v>
+        <v>0.02717693426506614</v>
       </c>
       <c r="BF37" t="n">
-        <v>0.04873294763979857</v>
+        <v>0.02717693426506614</v>
       </c>
       <c r="BG37" t="n">
-        <v>0.8311507449090484</v>
+        <v>0.9058377272758142</v>
       </c>
       <c r="BH37" t="n">
-        <v>0.1295715685606994</v>
+        <v>0.1072367792580692</v>
       </c>
       <c r="BI37" t="n">
-        <v>0.5510621890933358</v>
+        <v>0.6284474637177389</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.06387624374734133</v>
+        <v>0.02933323546261961</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.743557085531996</v>
+        <v>0.8822363377758342</v>
       </c>
       <c r="BL37" t="n">
-        <v>0.06387624374734133</v>
+        <v>0.02933323546261961</v>
       </c>
       <c r="BM37" t="n">
-        <v>0.06387624374734133</v>
+        <v>0.02933323546261961</v>
       </c>
       <c r="BN37" t="n">
-        <v>0.743557085531996</v>
+        <v>0.8822363377758342</v>
       </c>
       <c r="BO37" t="n">
-        <v>0.1075224735732624</v>
+        <v>0.08922822667599405</v>
       </c>
       <c r="BP37" t="n">
-        <v>0.5683312781665562</v>
+        <v>0.6417768929539471</v>
       </c>
       <c r="BQ37" t="n">
-        <v>54.06273579823565</v>
+        <v>54.8924137296472</v>
       </c>
       <c r="BR37" t="n">
-        <v>0.8461279237587604</v>
+        <v>0.8437665141106383</v>
       </c>
       <c r="BS37" t="n">
-        <v>54.06273579823565</v>
+        <v>54.8924137296472</v>
       </c>
       <c r="BT37" t="n">
-        <v>54.06273579823565</v>
+        <v>54.8924137296472</v>
       </c>
       <c r="BU37" t="n">
-        <v>0.8461279237587604</v>
+        <v>0.8437665141106383</v>
       </c>
       <c r="BV37" t="n">
-        <v>384.8816254370847</v>
+        <v>378.370028110039</v>
       </c>
       <c r="BW37" t="n">
-        <v>-0.09544095278729969</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46078.97717592592</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>02-25_23-27-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Best (Lowest Val Loss)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>data/reduce_row_number_absolutes</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>16590</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>motion</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>multihead</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>3</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>compact</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>[2, 3, 2]</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>spsa</t>
-        </is>
-      </c>
-      <c r="Z38" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="n">
-        <v>1024</v>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>[0.01, 0.0005]</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.1591133164993049</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>23.76731130572179</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.3623696602491133</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>-0.2203559043159494</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>26.80419074319915</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0.4078973530980483</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>26.80419074319915</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>26.80419074319915</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.4078973530980483</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>107.7487677249886</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>-0.1920405892999608</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.1084906814355005</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0.2122173788256562</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.1084906814355005</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.1084906814355005</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0.2122173788256562</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0.1915399417630574</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>-0.3908276304024336</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0.1317838071242491</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0.5433972549649968</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0.1317838071242491</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0.1317838071242491</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0.5433972549649968</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0.3059189854267712</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>-0.05994394571170436</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0.2042832674402151</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>0.1798672964141548</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.2042832674402151</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>0.2042832674402151</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>0.1798672964141548</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>0.2722240578063271</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>-0.09289348710437562</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>106.7722052167969</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>0.6961074821873809</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>106.7722052167969</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>106.7722052167969</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>0.6961074821873809</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>430.2253879149575</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>-0.2244972939813314</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46079.68121527778</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>02-26_16-20-57_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Final (Last Iteration)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>data/reduce_row_number_absolutes</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>16590</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>5</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>motion</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>multihead</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>compact</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>[2, 3, 2]</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>spsa</t>
-        </is>
-      </c>
-      <c r="Z39" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="n">
-        <v>1024</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[0.01, 0.0005]</t>
-        </is>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.1535401410543428</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>28.63624293399343</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.3673070524240782</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>-0.1850266394329405</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>32.44398207201748</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0.4132439460318347</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>32.44398207201748</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>32.44398207201748</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.4132439460318347</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>92.76904123264814</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>-0.1310563136572235</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.1104287051895017</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0.1981448205872527</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0.1104287051895017</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.1104287051895017</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0.1981448205872527</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0.1668428776538589</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>-0.2114950126898054</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0.1041841981164686</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0.6390240053969665</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0.1041841981164686</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0.1041841981164686</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0.6390240053969665</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0.3220556819463247</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>-0.1158541526438668</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0.2032581565968143</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0.1839827922058968</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.2032581565968143</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>0.2032581565968143</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0.1839827922058968</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0.2846873523675547</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>-0.142929672603894</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>129.358057228167</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0.6318241659372197</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>129.358057228167</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>129.358057228167</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>0.6318241659372197</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>370.3025790186248</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>-0.05394641669134725</v>
+        <v>-0.07690779893251198</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/experiments_summary.xlsx
+++ b/logs/final_winner_optimization/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW41"/>
+  <dimension ref="A1:BW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11407,6 +11407,536 @@
       </c>
       <c r="BW41" t="n">
         <v>0.3440918543692277</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46083.52623842593</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>03-02_12-37-47_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>768</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[0.03, 0.003]</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.106683813375779</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>12.14895909929622</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.6893791908115605</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-0.1550389162358879</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>14.90291476964044</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.6971142888494368</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>14.90291476964044</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>14.90291476964044</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.6971142888494368</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>84.09300147472879</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>-0.04860209473589239</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.05871871373526867</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.5736262174198179</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.05871871373526867</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.05871871373526867</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.5736262174198179</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.2285028332516925</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>-0.6592260140959803</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.05539199637486079</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.8080785632950769</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0.05539199637486079</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0.05539199637486079</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.8080785632950769</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0.2271210355248297</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0.2130741208739337</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0.5757921469521483</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0.1056640784052614</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0.5757921469521483</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0.1974604512117032</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0.2072587455018606</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>59.39188429004646</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0.8309602277307033</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>59.39188429004646</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>59.39188429004646</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0.8309602277307033</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>335.7189215789264</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>0.04448476877662633</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46083.96429398148</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>03-02_23-08-35_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>768</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[0.03, 0.003]</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.09888482227899612</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>11.87657318600668</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.7188551229838736</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-0.03278269462894498</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>14.46762963668539</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.7288667713880903</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>14.46762963668539</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>14.46762963668539</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.7288667713880903</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>88.1900720770963</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.06582615877991738</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.05351542574924598</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0.6114088158339581</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.05351542574924598</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.05351542574924598</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.6114088158339581</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0.1164453542986079</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0.154456168777319</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.04121408708402952</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0.8572019908414316</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0.04121408708402952</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0.04121408708402952</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0.8572019908414316</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0.2626723747824426</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0.08989632347283116</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0.0968891782689842</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0.6110205954816734</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0.0968891782689842</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0.0968891782689842</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0.6110205954816734</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0.2438057181324194</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0.02119715791139254</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>57.67889985563927</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0.835835683395301</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>57.67889985563927</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>57.67889985563927</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0.835835683395301</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>352.137364861172</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>-0.002245015041872467</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/experiments_summary.xlsx
+++ b/logs/final_winner_optimization/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW43"/>
+  <dimension ref="A1:BW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11937,6 +11937,1066 @@
       </c>
       <c r="BW43" t="n">
         <v>-0.002245015041872467</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46084.27708333333</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>03-03_06-39-00_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>768</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>[0.03, 0.003]</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.1050930187693029</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>15.96120310929299</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.6724279987993795</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-0.1654553245378115</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>19.29548834930062</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.6917473300343834</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>19.29548834930062</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>19.29548834930062</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.6917473300343834</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>113.8751458573673</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>-0.05654148827777775</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV44" t="n">
+        <v>0.07847716638509727</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.4301543043220557</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.07847716638509727</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0.07847716638509727</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.4301543043220557</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0.1690041711581517</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>-0.2271887979938556</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.04445140078596294</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0.8459853902962023</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0.04445140078596294</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.04445140078596294</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0.8459853902962023</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0.2355491333979729</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>0.1838725618335837</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>0.07224290722181194</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>0.7099675780735906</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.07224290722181194</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>0.07224290722181194</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>0.7099675780735906</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0.2212368238309205</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0.1118041299476531</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>76.98678192280968</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>0.7808820474456852</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>76.98678192280968</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>76.98678192280968</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>0.7808820474456852</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>454.8747933010825</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>-0.2946538468984858</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46084.61413194444</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>03-03_14-44-21_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>768</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[0.03, 0.003]</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.1080346934807675</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>14.65193509352135</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.6661981127356983</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>-0.08456976885951897</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>21.86151300287629</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.652274489910897</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>21.86151300287629</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>21.86151300287629</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.652274489910897</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>112.9420027161099</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>-0.05544585656819831</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV45" t="n">
+        <v>0.0714066584151385</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0.481495334057588</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0.0714066584151385</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0.0714066584151385</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0.481495334057588</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0.235408170133111</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>-0.7093676881693423</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0.06322711296634731</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0.7809315577455327</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0.06322711296634731</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0.06322711296634731</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0.7809315577455327</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0.1814450989638859</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>0.3713314854992269</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>0.1009076869194331</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>0.594887554312062</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.1009076869194331</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>0.1009076869194331</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>0.594887554312062</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0.1493386164843525</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0.4004526909041852</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>87.21051055320396</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>0.7517835135284077</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>87.21051055320396</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>87.21051055320396</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>0.7517835135284077</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>451.2018189788577</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>-0.2841999145068523</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46085.00217592593</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>03-04_00-03-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>768</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[0.03, 0.003]</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.1295562246915034</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>15.1927683907798</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.5496106601849829</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-0.1289235536888186</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>19.31265694774851</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.5545593758441881</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>19.31265694774851</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>19.31265694774851</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.5545593758441881</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>118.4515644245869</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>-0.1596832277240472</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV46" t="n">
+        <v>0.1127215688069107</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0.181495666147278</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0.1127215688069107</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0.1127215688069107</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0.181495666147278</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0.1591132707498557</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>-0.1553680725055178</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0.07778456733806562</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0.7304930875579061</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0.07778456733806562</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0.07778456733806562</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0.7304930875579061</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0.3102149775819534</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>-0.07482864098276809</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>0.1182561749793233</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>0.5252388621114223</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>0.1182561749793233</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0.1182561749793233</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>0.5252388621114223</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0.2645510569058612</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>-0.06208881547380551</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>76.94186547986962</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>0.7810098875601469</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>76.94186547986962</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>76.94186547986962</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>0.7810098875601469</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>473.0723783931136</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>-0.346447381934107</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46085.32609953704</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>03-04_07-49-35_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[0.05, 0.0001]</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.07802924956506903</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>10.48054074212451</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.7649953577781813</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-0.1352599590373447</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>13.48052851535376</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.7624088776905147</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>13.48052851535376</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>13.48052851535376</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.7624088776905147</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>98.56331662872141</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>-0.0512762418029323</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV47" t="n">
+        <v>0.042145360771735</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0.6939701885932523</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.042145360771735</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.042145360771735</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0.6939701885932523</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0.2300120987006954</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-0.6701852326733868</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0.04791062384724636</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0.8339999212166727</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0.04791062384724636</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0.04791062384724636</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0.8339999212166727</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0.2038867823385259</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>0.2935758457459606</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>0.08103994005183371</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>0.6746502737792943</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0.08103994005183371</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>0.08103994005183371</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>0.6746502737792943</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0.1763820777424799</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>0.2918817478511132</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>53.75101813674419</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>0.8470151271728414</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>53.75101813674419</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>53.75101813674419</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>0.8470151271728414</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>393.6429855561051</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>-0.1203773281354161</v>
       </c>
     </row>
   </sheetData>

--- a/logs/final_winner_optimization/experiments_summary.xlsx
+++ b/logs/final_winner_optimization/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW47"/>
+  <dimension ref="A1:BW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12997,6 +12997,801 @@
       </c>
       <c r="BW47" t="n">
         <v>-0.1203773281354161</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46085.59322916667</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>03-04_14-14-15_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>[0.05, 0.0001]</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.0688618667531352</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>9.583562204354951</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.7895707621960872</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.1867260167949384</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>11.95718005622282</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.7981323573928729</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>11.95718005622282</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>11.95718005622282</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.7981323573928729</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>71.91863557898208</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.2530134619383231</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV48" t="n">
+        <v>0.04296638765079115</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0.6880084718975934</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0.04296638765079115</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.04296638765079115</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0.6880084718975934</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0.1035975684120596</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0.2477477059680875</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0.03498156467388404</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0.8787963498379168</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0.03498156467388404</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0.03498156467388404</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0.8787963498379168</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0.2109588777335622</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0.2690725456745151</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>0.05941623395545763</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>0.7614626141368163</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0.05941623395545763</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>0.05941623395545763</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0.7614626141368163</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0.1712156149531613</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>0.3126234617882054</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>47.69135603861108</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>0.8642619936991655</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>47.69135603861108</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>47.69135603861108</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>0.8642619936991655</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>287.18877025483</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>0.182610134322481</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46085.88435185186</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03-04_21-13-28_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>3</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>[0.05, 0.0001]</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.07419820570411019</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>12.96923574920233</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.7578659912293069</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-0.2555740921623109</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>15.77922734055479</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.7697312645606686</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>15.77922734055479</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>15.77922734055479</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.7697312645606686</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>118.4743665401534</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>-0.1491931009169778</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV49" t="n">
+        <v>0.06134868607458734</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0.5545292177911795</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0.06134868607458734</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0.06134868607458734</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0.5545292177911795</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0.2309898427035444</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>-0.6772849183165248</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0.03319135360437299</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0.8849990488368925</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0.03319135360437299</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0.03319135360437299</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0.8849990488368925</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0.2188420949913155</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>0.2417588815897939</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>0.04517392211113919</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>0.818640991321389</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>0.04517392211113919</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>0.04517392211113919</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>0.818640991321389</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0.2028324767243428</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0.1856917622505154</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>62.977195400429</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>0.8207558002932123</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>62.977195400429</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>62.977195400429</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>0.8207558002932123</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>473.2448017461955</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>-0.3469381291917044</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46086.14479166667</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>03-05_03-28-30_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[['wv', 'sv', 'rarad'], ['sv', 'yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>['effsu2', 'effsu2', 'realamplitudes']</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>[2, 3, 2]</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>[[0, 1, 2], [0, 1, 2], [0, 1, -1]]</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>[0.05, 0.0001]</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.07900416701343374</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>11.40153630673874</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.7555643148997051</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-0.147127665579905</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>19.9078231520243</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0.7283214983078622</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>19.9078231520243</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>19.9078231520243</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.7283214983078622</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>98.11610278894445</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>-0.02310761739814438</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV50" t="n">
+        <v>0.05284324896903466</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0.6162896883549978</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0.05284324896903466</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.05284324896903466</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0.6162896883549978</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.2841851157132149</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>-1.063551379649031</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0.04933045706436691</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0.8290805023701835</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0.04933045706436691</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0.04933045706436691</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0.8290805023701835</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0.1303605701015614</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0.5483284672707845</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0.07620705077703777</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0.6940527955655165</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0.07620705077703777</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0.07620705077703777</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0.6940527955655165</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0.1150008012961386</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>0.5383081577685118</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>79.4529118512866</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0.7738630069407504</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>79.4529118512866</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>79.4529118512866</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>0.7738630069407504</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>391.9348646686658</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>-0.1155157149828334</v>
       </c>
     </row>
   </sheetData>
